--- a/EXPARK_raw data.xlsx
+++ b/EXPARK_raw data.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vfnpraha-my.sharepoint.com/personal/103648_vfn_cz/Documents/Články/EXPARK/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{9D9F1D77-B3BB-476C-8D22-42142E399600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90185843-8273-4C14-97F9-CAB66B0B126F}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{80BEA703-514F-B74C-9FCD-F033127E333F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01CD32BC-F47A-4DF8-950B-9BE28C47EB89}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{272887D9-2FC4-4E37-8F6D-5B460D11608A}"/>
+    <workbookView xWindow="28815" yWindow="225" windowWidth="24150" windowHeight="15255" xr2:uid="{272887D9-2FC4-4E37-8F6D-5B460D11608A}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
@@ -312,6 +312,72 @@
   </si>
   <si>
     <t xml:space="preserve">Pozn. pacient 20 vyřazen z analýzy, protože se u něj změnila významně léčba Parkinsonovy nemoci. </t>
+  </si>
+  <si>
+    <t>Normalizace OI_EXP1_1pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace OI_EXP1_2pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace OI_EXP1_3pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace OI_EXP2_1pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace OI_EXP2_2pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace OI_EXP2_3pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace OE_EXP1_1pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace OE_EXP1_2pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace OE_EXP1_3pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace OE_EXP2_1pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace OE_EXP2_2pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace OE_EXP2_3pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace RA_EXP1_1pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace RA_EXP1_2pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace RA_EXP1_3pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace RA_EXP2_1pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace RA_EXP2_2pokus_ICC</t>
+  </si>
+  <si>
+    <t>Normalizace RA_EXP2_3pokus_ICC</t>
+  </si>
+  <si>
+    <t>Korelace OE_vizita 1</t>
+  </si>
+  <si>
+    <t>Korelace OI_vizita 1</t>
+  </si>
+  <si>
+    <t>Korelace OI_vizita 2</t>
+  </si>
+  <si>
+    <t>Korelace OE_vizita 2</t>
   </si>
 </sst>
 </file>
@@ -360,7 +426,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,6 +448,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -529,7 +601,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -558,6 +629,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -594,6 +669,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -928,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64C23291-0991-461F-ADF5-F3F7D9DE7461}">
-  <dimension ref="A1:BQ42"/>
+  <dimension ref="A1:CM96"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="12.140625" customWidth="1"/>
@@ -989,15 +1065,34 @@
     <col min="60" max="60" width="2.85546875" customWidth="1"/>
     <col min="61" max="61" width="25.28515625" customWidth="1"/>
     <col min="62" max="62" width="23.85546875" customWidth="1"/>
-    <col min="63" max="63" width="22.5703125" customWidth="1"/>
+    <col min="63" max="63" width="22.42578125" customWidth="1"/>
     <col min="64" max="64" width="23.42578125" customWidth="1"/>
     <col min="65" max="65" width="23" customWidth="1"/>
-    <col min="66" max="66" width="5.7109375" customWidth="1"/>
-    <col min="67" max="67" width="33.7109375" customWidth="1"/>
-    <col min="68" max="68" width="33.42578125" customWidth="1"/>
+    <col min="66" max="66" width="4" customWidth="1"/>
+    <col min="67" max="70" width="23" customWidth="1"/>
+    <col min="71" max="71" width="5.7109375" customWidth="1"/>
+    <col min="72" max="72" width="33.7109375" customWidth="1"/>
+    <col min="73" max="73" width="33.42578125" customWidth="1"/>
+    <col min="74" max="74" width="29" customWidth="1"/>
+    <col min="75" max="75" width="30.140625" customWidth="1"/>
+    <col min="76" max="77" width="29" customWidth="1"/>
+    <col min="78" max="78" width="30.140625" customWidth="1"/>
+    <col min="79" max="79" width="29" customWidth="1"/>
+    <col min="80" max="80" width="25.140625" customWidth="1"/>
+    <col min="81" max="81" width="31.85546875" customWidth="1"/>
+    <col min="82" max="82" width="33.140625" customWidth="1"/>
+    <col min="83" max="83" width="31.42578125" customWidth="1"/>
+    <col min="84" max="84" width="29.42578125" customWidth="1"/>
+    <col min="85" max="85" width="30" customWidth="1"/>
+    <col min="86" max="86" width="31.42578125" customWidth="1"/>
+    <col min="87" max="87" width="31.28515625" customWidth="1"/>
+    <col min="88" max="88" width="30.42578125" customWidth="1"/>
+    <col min="89" max="89" width="33.28515625" customWidth="1"/>
+    <col min="90" max="90" width="35.140625" customWidth="1"/>
+    <col min="91" max="91" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:91" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1063,7 +1158,7 @@
       <c r="W1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="32"/>
+      <c r="X1" s="35"/>
       <c r="Y1" s="1" t="s">
         <v>21</v>
       </c>
@@ -1079,7 +1174,7 @@
       <c r="AC1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AD1" s="32"/>
+      <c r="AD1" s="35"/>
       <c r="AE1" s="1" t="s">
         <v>26</v>
       </c>
@@ -1095,7 +1190,7 @@
       <c r="AI1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AJ1" s="32"/>
+      <c r="AJ1" s="35"/>
       <c r="AK1" s="1" t="s">
         <v>31</v>
       </c>
@@ -1125,7 +1220,7 @@
       <c r="AU1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AV1" s="32"/>
+      <c r="AV1" s="35"/>
       <c r="AW1" s="1" t="s">
         <v>39</v>
       </c>
@@ -1141,7 +1236,7 @@
       <c r="BA1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="32"/>
+      <c r="BB1" s="35"/>
       <c r="BC1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1157,7 +1252,7 @@
       <c r="BG1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BH1" s="32"/>
+      <c r="BH1" s="35"/>
       <c r="BI1" s="1" t="s">
         <v>49</v>
       </c>
@@ -1173,17 +1268,84 @@
       <c r="BM1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BN1" s="26" t="s">
+      <c r="BN1" s="26"/>
+      <c r="BO1" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="BP1" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="BQ1" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="BR1" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="BS1" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="BO1" s="3" t="s">
+      <c r="BT1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="BP1" s="3" t="s">
+      <c r="BU1" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BV1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CB1" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="CC1" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="CD1" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="CE1" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF1" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="CG1" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="CH1" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="CI1" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="CJ1" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="CK1" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="CL1" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="CM1" s="41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:91" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1233,13 +1395,13 @@
       <c r="Q2" s="1">
         <v>8</v>
       </c>
-      <c r="R2" s="29" t="s">
+      <c r="R2" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="11">
         <v>6</v>
       </c>
-      <c r="T2" s="29" t="s">
+      <c r="T2" s="32" t="s">
         <v>59</v>
       </c>
       <c r="U2" s="1">
@@ -1251,105 +1413,105 @@
       <c r="W2" s="1">
         <v>0.05</v>
       </c>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="10">
+      <c r="X2" s="36"/>
+      <c r="Y2" s="9">
         <v>1.8599999999999998E-2</v>
       </c>
-      <c r="Z2" s="10">
+      <c r="Z2" s="9">
         <v>2.0060000000000001E-2</v>
       </c>
-      <c r="AA2" s="10">
+      <c r="AA2" s="9">
         <v>1.668E-2</v>
       </c>
-      <c r="AB2" s="10">
+      <c r="AB2" s="9">
         <v>2.1520000000000001E-2</v>
       </c>
-      <c r="AC2" s="10">
+      <c r="AC2" s="9">
         <v>2.4280000000000003E-2</v>
       </c>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="10">
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="9">
         <v>7.2239999999999999E-2</v>
       </c>
-      <c r="AF2" s="10">
+      <c r="AF2" s="9">
         <v>6.6040000000000001E-2</v>
       </c>
-      <c r="AG2" s="10">
+      <c r="AG2" s="9">
         <v>7.4380000000000002E-2</v>
       </c>
-      <c r="AH2" s="10">
+      <c r="AH2" s="9">
         <v>6.336E-2</v>
       </c>
-      <c r="AI2" s="10">
+      <c r="AI2" s="9">
         <v>6.5939999999999999E-2</v>
       </c>
-      <c r="AJ2" s="33"/>
-      <c r="AK2" s="10">
+      <c r="AJ2" s="36"/>
+      <c r="AK2" s="9">
         <v>6.8879999999999997E-2</v>
       </c>
-      <c r="AL2" s="10">
+      <c r="AL2" s="9">
         <v>6.9199999999999998E-2</v>
       </c>
-      <c r="AM2" s="10">
+      <c r="AM2" s="9">
         <v>5.6779999999999997E-2</v>
       </c>
-      <c r="AN2" s="10">
+      <c r="AN2" s="9">
         <v>6.4860000000000001E-2</v>
       </c>
-      <c r="AO2" s="10">
+      <c r="AO2" s="9">
         <v>5.6599999999999998E-2</v>
       </c>
-      <c r="AP2" s="29" t="s">
+      <c r="AP2" s="32" t="s">
         <v>60</v>
       </c>
       <c r="AQ2" s="8">
         <v>5</v>
       </c>
-      <c r="AR2" s="35" t="s">
+      <c r="AR2" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="AS2" s="13">
+      <c r="AS2" s="12">
         <v>1.2766666666666667E-2</v>
       </c>
-      <c r="AT2" s="13">
+      <c r="AT2" s="12">
         <v>5.4166666666666662E-2</v>
       </c>
-      <c r="AU2" s="13">
+      <c r="AU2" s="12">
         <v>3.2566666666666667E-2</v>
       </c>
-      <c r="AV2" s="33"/>
-      <c r="AW2" s="10">
+      <c r="AV2" s="36"/>
+      <c r="AW2" s="9">
         <v>3.456E-2</v>
       </c>
-      <c r="AX2" s="10">
+      <c r="AX2" s="9">
         <v>2.1059999999999999E-2</v>
       </c>
-      <c r="AY2" s="10">
+      <c r="AY2" s="9">
         <v>1.7979999999999999E-2</v>
       </c>
-      <c r="AZ2" s="10">
+      <c r="AZ2" s="9">
         <v>1.796E-2</v>
       </c>
-      <c r="BA2" s="10">
+      <c r="BA2" s="9">
         <v>1.9020000000000002E-2</v>
       </c>
-      <c r="BB2" s="33"/>
-      <c r="BC2" s="10">
+      <c r="BB2" s="36"/>
+      <c r="BC2" s="9">
         <v>7.9659999999999995E-2</v>
       </c>
-      <c r="BD2" s="10">
+      <c r="BD2" s="9">
         <v>0.10958</v>
       </c>
-      <c r="BE2" s="10">
+      <c r="BE2" s="9">
         <v>0.10285999999999999</v>
       </c>
-      <c r="BF2" s="10">
+      <c r="BF2" s="9">
         <v>0.13222</v>
       </c>
-      <c r="BG2" s="10">
+      <c r="BG2" s="9">
         <v>0.1113</v>
       </c>
-      <c r="BH2" s="33"/>
+      <c r="BH2" s="36"/>
       <c r="BI2" s="1">
         <v>5.484E-2</v>
       </c>
@@ -1366,14 +1528,81 @@
         <v>7.1480000000000002E-2</v>
       </c>
       <c r="BN2" s="27"/>
-      <c r="BO2" s="11">
+      <c r="BO2" s="9">
+        <v>6.8879999999999997E-2</v>
+      </c>
+      <c r="BP2" s="9">
+        <v>7.2239999999999999E-2</v>
+      </c>
+      <c r="BQ2" s="1">
+        <v>5.484E-2</v>
+      </c>
+      <c r="BR2" s="9">
+        <v>7.9659999999999995E-2</v>
+      </c>
+      <c r="BS2" s="30"/>
+      <c r="BT2" s="10">
         <v>0.129108</v>
       </c>
-      <c r="BP2" s="11">
+      <c r="BU2" s="10">
         <v>0.129108</v>
       </c>
-    </row>
-    <row r="3" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BV2" s="9">
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="BW2" s="9">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="BX2" s="9">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="BY2" s="9">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="BZ2" s="9">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="CA2" s="9">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="CB2" s="9">
+        <v>6.3E-2</v>
+      </c>
+      <c r="CC2" s="9">
+        <v>6.5299999999999997E-2</v>
+      </c>
+      <c r="CD2" s="9">
+        <v>7.2099999999999997E-2</v>
+      </c>
+      <c r="CE2" s="9">
+        <v>6.7199999999999996E-2</v>
+      </c>
+      <c r="CF2" s="9">
+        <v>5.3699999999999998E-2</v>
+      </c>
+      <c r="CG2" s="9">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="CH2" s="9">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="CI2" s="9">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="CJ2" s="9">
+        <v>1.43E-2</v>
+      </c>
+      <c r="CK2" s="9">
+        <v>1.4E-2</v>
+      </c>
+      <c r="CL2" s="9">
+        <v>1.66E-2</v>
+      </c>
+      <c r="CM2" s="9">
+        <v>7.7000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1423,53 +1652,53 @@
       <c r="Q3" s="1">
         <v>9</v>
       </c>
-      <c r="R3" s="30"/>
-      <c r="S3" s="12">
+      <c r="R3" s="33"/>
+      <c r="S3" s="11">
         <v>0</v>
       </c>
-      <c r="T3" s="30"/>
-      <c r="U3" s="13">
+      <c r="T3" s="33"/>
+      <c r="U3" s="12">
         <v>1.7066666666666664E-2</v>
       </c>
-      <c r="V3" s="13">
+      <c r="V3" s="12">
         <v>5.0466666666666667E-2</v>
       </c>
-      <c r="W3" s="13">
+      <c r="W3" s="12">
         <v>5.4866666666666675E-2</v>
       </c>
-      <c r="X3" s="33"/>
-      <c r="Y3" s="10">
+      <c r="X3" s="36"/>
+      <c r="Y3" s="9">
         <v>1.498E-2</v>
       </c>
-      <c r="Z3" s="10">
+      <c r="Z3" s="9">
         <v>1.452E-2</v>
       </c>
-      <c r="AA3" s="10">
+      <c r="AA3" s="9">
         <v>1.328E-2</v>
       </c>
-      <c r="AB3" s="10">
+      <c r="AB3" s="9">
         <v>1.188E-2</v>
       </c>
-      <c r="AC3" s="10">
+      <c r="AC3" s="9">
         <v>1.5520000000000001E-2</v>
       </c>
-      <c r="AD3" s="33"/>
-      <c r="AE3" s="10">
+      <c r="AD3" s="36"/>
+      <c r="AE3" s="9">
         <v>4.2380000000000001E-2</v>
       </c>
-      <c r="AF3" s="10">
+      <c r="AF3" s="9">
         <v>3.918E-2</v>
       </c>
-      <c r="AG3" s="10">
+      <c r="AG3" s="9">
         <v>4.0379999999999999E-2</v>
       </c>
-      <c r="AH3" s="10">
+      <c r="AH3" s="9">
         <v>3.4139999999999997E-2</v>
       </c>
-      <c r="AI3" s="10">
+      <c r="AI3" s="9">
         <v>4.2100000000000005E-2</v>
       </c>
-      <c r="AJ3" s="33"/>
+      <c r="AJ3" s="36"/>
       <c r="AK3" s="1">
         <v>4.41E-2</v>
       </c>
@@ -1485,53 +1714,53 @@
       <c r="AO3" s="1">
         <v>5.1239999999999994E-2</v>
       </c>
-      <c r="AP3" s="30"/>
+      <c r="AP3" s="33"/>
       <c r="AQ3" s="3">
         <v>1</v>
       </c>
-      <c r="AR3" s="36"/>
-      <c r="AS3" s="13">
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="12">
         <v>1.7033333333333334E-2</v>
       </c>
-      <c r="AT3" s="13">
+      <c r="AT3" s="12">
         <v>6.0066666666666657E-2</v>
       </c>
-      <c r="AU3" s="13">
+      <c r="AU3" s="12">
         <v>6.9066666666666665E-2</v>
       </c>
-      <c r="AV3" s="33"/>
-      <c r="AW3" s="10">
+      <c r="AV3" s="36"/>
+      <c r="AW3" s="9">
         <v>1.6379999999999999E-2</v>
       </c>
-      <c r="AX3" s="10">
+      <c r="AX3" s="9">
         <v>1.7860000000000001E-2</v>
       </c>
-      <c r="AY3" s="10">
+      <c r="AY3" s="9">
         <v>1.8259999999999998E-2</v>
       </c>
-      <c r="AZ3" s="10">
+      <c r="AZ3" s="9">
         <v>1.6660000000000001E-2</v>
       </c>
-      <c r="BA3" s="10">
+      <c r="BA3" s="9">
         <v>1.532E-2</v>
       </c>
-      <c r="BB3" s="33"/>
-      <c r="BC3" s="10">
+      <c r="BB3" s="36"/>
+      <c r="BC3" s="9">
         <v>4.1820000000000003E-2</v>
       </c>
-      <c r="BD3" s="10">
+      <c r="BD3" s="9">
         <v>4.99E-2</v>
       </c>
-      <c r="BE3" s="10">
+      <c r="BE3" s="9">
         <v>5.842E-2</v>
       </c>
-      <c r="BF3" s="10">
+      <c r="BF3" s="9">
         <v>4.6820000000000001E-2</v>
       </c>
-      <c r="BG3" s="10">
+      <c r="BG3" s="9">
         <v>4.8760000000000005E-2</v>
       </c>
-      <c r="BH3" s="33"/>
+      <c r="BH3" s="36"/>
       <c r="BI3" s="1">
         <v>8.6879999999999999E-2</v>
       </c>
@@ -1548,14 +1777,81 @@
         <v>9.8820000000000005E-2</v>
       </c>
       <c r="BN3" s="27"/>
-      <c r="BO3" s="10">
+      <c r="BO3" s="1">
+        <v>4.41E-2</v>
+      </c>
+      <c r="BP3" s="9">
+        <v>4.2380000000000001E-2</v>
+      </c>
+      <c r="BQ3" s="1">
+        <v>8.6879999999999999E-2</v>
+      </c>
+      <c r="BR3" s="9">
+        <v>4.1820000000000003E-2</v>
+      </c>
+      <c r="BS3" s="30"/>
+      <c r="BT3" s="9">
         <v>7.5971999999999998E-2</v>
       </c>
-      <c r="BP3" s="10">
+      <c r="BU3" s="9">
         <v>7.5971999999999998E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BV3" s="9">
+        <v>5.8400000000000001E-2</v>
+      </c>
+      <c r="BW3" s="9">
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="BX3" s="9">
+        <v>6.1100000000000002E-2</v>
+      </c>
+      <c r="BY3" s="9">
+        <v>7.0199999999999999E-2</v>
+      </c>
+      <c r="BZ3" s="9">
+        <v>5.5300000000000002E-2</v>
+      </c>
+      <c r="CA3" s="9">
+        <v>8.1699999999999995E-2</v>
+      </c>
+      <c r="CB3" s="9">
+        <v>4.9599999999999998E-2</v>
+      </c>
+      <c r="CC3" s="9">
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="CD3" s="9">
+        <v>5.67E-2</v>
+      </c>
+      <c r="CE3" s="9">
+        <v>6.3299999999999995E-2</v>
+      </c>
+      <c r="CF3" s="9">
+        <v>5.0700000000000002E-2</v>
+      </c>
+      <c r="CG3" s="9">
+        <v>6.6199999999999995E-2</v>
+      </c>
+      <c r="CH3" s="9">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="CI3" s="9">
+        <v>1.9E-2</v>
+      </c>
+      <c r="CJ3" s="9">
+        <v>2.24E-2</v>
+      </c>
+      <c r="CK3" s="9">
+        <v>1.49E-2</v>
+      </c>
+      <c r="CL3" s="9">
+        <v>1.35E-2</v>
+      </c>
+      <c r="CM3" s="9">
+        <v>2.2700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1605,53 +1901,53 @@
       <c r="Q4" s="1">
         <v>3</v>
       </c>
-      <c r="R4" s="30"/>
-      <c r="S4" s="12">
+      <c r="R4" s="33"/>
+      <c r="S4" s="11">
         <v>6</v>
       </c>
-      <c r="T4" s="30"/>
-      <c r="U4" s="13">
+      <c r="T4" s="33"/>
+      <c r="U4" s="12">
         <v>3.09E-2</v>
       </c>
-      <c r="V4" s="13">
+      <c r="V4" s="12">
         <v>6.2866666666666668E-2</v>
       </c>
-      <c r="W4" s="13">
+      <c r="W4" s="12">
         <v>2.7133333333333332E-2</v>
       </c>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="10">
+      <c r="X4" s="36"/>
+      <c r="Y4" s="9">
         <v>2.222E-2</v>
       </c>
-      <c r="Z4" s="10">
+      <c r="Z4" s="9">
         <v>1.43E-2</v>
       </c>
-      <c r="AA4" s="10">
+      <c r="AA4" s="9">
         <v>1.634E-2</v>
       </c>
-      <c r="AB4" s="10">
+      <c r="AB4" s="9">
         <v>1.4760000000000001E-2</v>
       </c>
-      <c r="AC4" s="10">
+      <c r="AC4" s="9">
         <v>1.44E-2</v>
       </c>
-      <c r="AD4" s="33"/>
-      <c r="AE4" s="10">
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="9">
         <v>7.3859999999999995E-2</v>
       </c>
-      <c r="AF4" s="10">
+      <c r="AF4" s="9">
         <v>6.6180000000000003E-2</v>
       </c>
-      <c r="AG4" s="10">
+      <c r="AG4" s="9">
         <v>7.0940000000000003E-2</v>
       </c>
-      <c r="AH4" s="10">
+      <c r="AH4" s="9">
         <v>6.0319999999999999E-2</v>
       </c>
-      <c r="AI4" s="10">
+      <c r="AI4" s="9">
         <v>6.6659999999999997E-2</v>
       </c>
-      <c r="AJ4" s="33"/>
+      <c r="AJ4" s="36"/>
       <c r="AK4" s="1">
         <v>2.53E-2</v>
       </c>
@@ -1667,53 +1963,53 @@
       <c r="AO4" s="1">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="AP4" s="30"/>
+      <c r="AP4" s="33"/>
       <c r="AQ4" s="3">
         <v>2</v>
       </c>
-      <c r="AR4" s="36"/>
-      <c r="AS4" s="14">
+      <c r="AR4" s="39"/>
+      <c r="AS4" s="13">
         <v>3.2400000000000005E-2</v>
       </c>
-      <c r="AT4" s="14">
+      <c r="AT4" s="13">
         <v>8.2799999999999999E-2</v>
       </c>
-      <c r="AU4" s="13">
+      <c r="AU4" s="12">
         <v>6.5166666666666664E-2</v>
       </c>
-      <c r="AV4" s="33"/>
-      <c r="AW4" s="10">
+      <c r="AV4" s="36"/>
+      <c r="AW4" s="9">
         <v>2.8840000000000001E-2</v>
       </c>
-      <c r="AX4" s="10">
+      <c r="AX4" s="9">
         <v>3.1800000000000002E-2</v>
       </c>
-      <c r="AY4" s="10">
+      <c r="AY4" s="9">
         <v>3.5040000000000002E-2</v>
       </c>
-      <c r="AZ4" s="10">
+      <c r="AZ4" s="9">
         <v>3.1980000000000001E-2</v>
       </c>
-      <c r="BA4" s="10">
+      <c r="BA4" s="9">
         <v>3.3059999999999999E-2</v>
       </c>
-      <c r="BB4" s="33"/>
-      <c r="BC4" s="10">
+      <c r="BB4" s="36"/>
+      <c r="BC4" s="9">
         <v>0.1071</v>
       </c>
-      <c r="BD4" s="10">
+      <c r="BD4" s="9">
         <v>0.11348</v>
       </c>
-      <c r="BE4" s="10">
+      <c r="BE4" s="9">
         <v>0.11126</v>
       </c>
-      <c r="BF4" s="10">
+      <c r="BF4" s="9">
         <v>0.10316</v>
       </c>
-      <c r="BG4" s="10">
+      <c r="BG4" s="9">
         <v>0.12090000000000001</v>
       </c>
-      <c r="BH4" s="33"/>
+      <c r="BH4" s="36"/>
       <c r="BI4" s="1">
         <v>4.6719999999999998E-2</v>
       </c>
@@ -1731,13 +2027,80 @@
       </c>
       <c r="BN4" s="27"/>
       <c r="BO4" s="1">
+        <v>2.53E-2</v>
+      </c>
+      <c r="BP4" s="9">
+        <v>7.3859999999999995E-2</v>
+      </c>
+      <c r="BQ4" s="1">
+        <v>4.6719999999999998E-2</v>
+      </c>
+      <c r="BR4" s="9">
+        <v>0.1071</v>
+      </c>
+      <c r="BS4" s="30"/>
+      <c r="BT4" s="1">
         <v>0.38129999999999997</v>
       </c>
-      <c r="BP4" s="10">
+      <c r="BU4" s="9">
         <v>0.38120400000000004</v>
       </c>
-    </row>
-    <row r="5" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BV4" s="9">
+        <v>6.5699999999999995E-2</v>
+      </c>
+      <c r="BW4" s="9">
+        <v>5.9200000000000003E-2</v>
+      </c>
+      <c r="BX4" s="9">
+        <v>7.0599999999999996E-2</v>
+      </c>
+      <c r="BY4" s="9">
+        <v>2.8799999999999999E-2</v>
+      </c>
+      <c r="BZ4" s="9">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="CA4" s="9">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="CB4" s="9">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="CC4" s="9">
+        <v>6.1199999999999997E-2</v>
+      </c>
+      <c r="CD4" s="9">
+        <v>6.4299999999999996E-2</v>
+      </c>
+      <c r="CE4" s="9">
+        <v>7.7299999999999994E-2</v>
+      </c>
+      <c r="CF4" s="9">
+        <v>8.6699999999999999E-2</v>
+      </c>
+      <c r="CG4" s="9">
+        <v>8.4400000000000003E-2</v>
+      </c>
+      <c r="CH4" s="9">
+        <v>2.98E-2</v>
+      </c>
+      <c r="CI4" s="9">
+        <v>2.3E-2</v>
+      </c>
+      <c r="CJ4" s="9">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="CK4" s="9">
+        <v>3.2800000000000003E-2</v>
+      </c>
+      <c r="CL4" s="9">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="CM4" s="9">
+        <v>2.7799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1787,115 +2150,115 @@
       <c r="Q5" s="1">
         <v>21</v>
       </c>
-      <c r="R5" s="30"/>
-      <c r="S5" s="12">
+      <c r="R5" s="33"/>
+      <c r="S5" s="11">
         <v>2</v>
       </c>
-      <c r="T5" s="30"/>
-      <c r="U5" s="13">
+      <c r="T5" s="33"/>
+      <c r="U5" s="12">
         <v>2.7866666666666668E-2</v>
       </c>
-      <c r="V5" s="13">
+      <c r="V5" s="12">
         <v>1.9933333333333334E-2</v>
       </c>
-      <c r="W5" s="13">
+      <c r="W5" s="12">
         <v>1.8333333333333333E-2</v>
       </c>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="10">
+      <c r="X5" s="36"/>
+      <c r="Y5" s="9">
         <v>2.75E-2</v>
       </c>
-      <c r="Z5" s="10">
+      <c r="Z5" s="9">
         <v>2.666E-2</v>
       </c>
-      <c r="AA5" s="10">
+      <c r="AA5" s="9">
         <v>2.01E-2</v>
       </c>
-      <c r="AB5" s="10">
+      <c r="AB5" s="9">
         <v>1.8419999999999999E-2</v>
       </c>
-      <c r="AC5" s="10">
+      <c r="AC5" s="9">
         <v>2.2440000000000002E-2</v>
       </c>
-      <c r="AD5" s="33"/>
-      <c r="AE5" s="10">
+      <c r="AD5" s="36"/>
+      <c r="AE5" s="9">
         <v>1.804E-2</v>
       </c>
-      <c r="AF5" s="10">
+      <c r="AF5" s="9">
         <v>1.788E-2</v>
       </c>
-      <c r="AG5" s="10">
+      <c r="AG5" s="9">
         <v>1.634E-2</v>
       </c>
-      <c r="AH5" s="10">
+      <c r="AH5" s="9">
         <v>1.506E-2</v>
       </c>
-      <c r="AI5" s="10">
+      <c r="AI5" s="9">
         <v>3.0000000000000006E-2</v>
       </c>
-      <c r="AJ5" s="33"/>
-      <c r="AK5" s="10">
+      <c r="AJ5" s="36"/>
+      <c r="AK5" s="9">
         <v>1.6580000000000001E-2</v>
       </c>
-      <c r="AL5" s="10">
+      <c r="AL5" s="9">
         <v>1.532E-2</v>
       </c>
-      <c r="AM5" s="10">
+      <c r="AM5" s="9">
         <v>1.218E-2</v>
       </c>
-      <c r="AN5" s="10">
+      <c r="AN5" s="9">
         <v>1.204E-2</v>
       </c>
-      <c r="AO5" s="10">
+      <c r="AO5" s="9">
         <v>1.4100000000000001E-2</v>
       </c>
-      <c r="AP5" s="30"/>
+      <c r="AP5" s="33"/>
       <c r="AQ5" s="3">
         <v>2</v>
       </c>
-      <c r="AR5" s="36"/>
-      <c r="AS5" s="14">
+      <c r="AR5" s="39"/>
+      <c r="AS5" s="13">
         <v>4.2300000000000004E-2</v>
       </c>
-      <c r="AT5" s="14">
+      <c r="AT5" s="13">
         <v>2.4799999999999999E-2</v>
       </c>
-      <c r="AU5" s="14">
+      <c r="AU5" s="13">
         <v>3.8800000000000001E-2</v>
       </c>
-      <c r="AV5" s="33"/>
-      <c r="AW5" s="10">
+      <c r="AV5" s="36"/>
+      <c r="AW5" s="9">
         <v>3.0020000000000002E-2</v>
       </c>
-      <c r="AX5" s="10">
+      <c r="AX5" s="9">
         <v>3.2800000000000003E-2</v>
       </c>
-      <c r="AY5" s="10">
+      <c r="AY5" s="9">
         <v>2.9960000000000001E-2</v>
       </c>
-      <c r="AZ5" s="10">
+      <c r="AZ5" s="9">
         <v>3.356E-2</v>
       </c>
-      <c r="BA5" s="10">
+      <c r="BA5" s="9">
         <v>2.7839999999999997E-2</v>
       </c>
-      <c r="BB5" s="33"/>
-      <c r="BC5" s="10">
+      <c r="BB5" s="36"/>
+      <c r="BC5" s="9">
         <v>2.3779999999999999E-2</v>
       </c>
-      <c r="BD5" s="10">
+      <c r="BD5" s="9">
         <v>2.605E-2</v>
       </c>
-      <c r="BE5" s="10">
+      <c r="BE5" s="9">
         <v>2.5100000000000001E-2</v>
       </c>
-      <c r="BF5" s="10">
+      <c r="BF5" s="9">
         <v>3.5520000000000003E-2</v>
       </c>
-      <c r="BG5" s="10">
+      <c r="BG5" s="9">
         <v>2.2449999999999998E-2</v>
       </c>
-      <c r="BH5" s="33"/>
+      <c r="BH5" s="36"/>
       <c r="BI5" s="1">
         <v>2.426E-2</v>
       </c>
@@ -1912,14 +2275,81 @@
         <v>2.104E-2</v>
       </c>
       <c r="BN5" s="27"/>
-      <c r="BO5" s="10">
+      <c r="BO5" s="9">
+        <v>1.6580000000000001E-2</v>
+      </c>
+      <c r="BP5" s="9">
+        <v>1.804E-2</v>
+      </c>
+      <c r="BQ5" s="1">
+        <v>2.426E-2</v>
+      </c>
+      <c r="BR5" s="9">
+        <v>2.3779999999999999E-2</v>
+      </c>
+      <c r="BS5" s="30"/>
+      <c r="BT5" s="9">
         <v>0.117788</v>
       </c>
-      <c r="BP5" s="10">
+      <c r="BU5" s="9">
         <v>0.117788</v>
       </c>
-    </row>
-    <row r="6" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BV5" s="9">
+        <v>2.46E-2</v>
+      </c>
+      <c r="BW5" s="9">
+        <v>1.29E-2</v>
+      </c>
+      <c r="BX5" s="9">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="BY5" s="9">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="BZ5" s="9">
+        <v>4.7300000000000002E-2</v>
+      </c>
+      <c r="CA5" s="9">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="CB5" s="9">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="CC5" s="9">
+        <v>2.07E-2</v>
+      </c>
+      <c r="CD5" s="9">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="CE5" s="9">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="CF5" s="9">
+        <v>2.76E-2</v>
+      </c>
+      <c r="CG5" s="9">
+        <v>2.3099999999999999E-2</v>
+      </c>
+      <c r="CH5" s="9">
+        <v>3.1800000000000002E-2</v>
+      </c>
+      <c r="CI5" s="9">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="CJ5" s="9">
+        <v>2.06E-2</v>
+      </c>
+      <c r="CK5" s="9">
+        <v>3.4700000000000002E-2</v>
+      </c>
+      <c r="CL5" s="9">
+        <v>5.57E-2</v>
+      </c>
+      <c r="CM5" s="9">
+        <v>3.6499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1969,115 +2399,115 @@
       <c r="Q6" s="1">
         <v>7</v>
       </c>
-      <c r="R6" s="30"/>
-      <c r="S6" s="12">
+      <c r="R6" s="33"/>
+      <c r="S6" s="11">
         <v>1</v>
       </c>
-      <c r="T6" s="30"/>
-      <c r="U6" s="13">
+      <c r="T6" s="33"/>
+      <c r="U6" s="12">
         <v>8.8666666666666668E-3</v>
       </c>
-      <c r="V6" s="13">
+      <c r="V6" s="12">
         <v>3.4833333333333334E-2</v>
       </c>
-      <c r="W6" s="13">
+      <c r="W6" s="12">
         <v>4.1300000000000003E-2</v>
       </c>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="10">
+      <c r="X6" s="36"/>
+      <c r="Y6" s="9">
         <v>7.2199999999999999E-3</v>
       </c>
-      <c r="Z6" s="10">
+      <c r="Z6" s="9">
         <v>6.62E-3</v>
       </c>
-      <c r="AA6" s="10">
+      <c r="AA6" s="9">
         <v>7.4599999999999996E-3</v>
       </c>
-      <c r="AB6" s="10">
+      <c r="AB6" s="9">
         <v>5.7600000000000004E-3</v>
       </c>
-      <c r="AC6" s="10">
+      <c r="AC6" s="9">
         <v>5.8399999999999997E-3</v>
       </c>
-      <c r="AD6" s="33"/>
-      <c r="AE6" s="10">
+      <c r="AD6" s="36"/>
+      <c r="AE6" s="9">
         <v>4.2380000000000001E-2</v>
       </c>
-      <c r="AF6" s="10">
+      <c r="AF6" s="9">
         <v>3.9800000000000002E-2</v>
       </c>
-      <c r="AG6" s="10">
+      <c r="AG6" s="9">
         <v>3.39E-2</v>
       </c>
-      <c r="AH6" s="10">
+      <c r="AH6" s="9">
         <v>3.3279999999999997E-2</v>
       </c>
-      <c r="AI6" s="10">
+      <c r="AI6" s="9">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="AJ6" s="33"/>
-      <c r="AK6" s="10">
+      <c r="AJ6" s="36"/>
+      <c r="AK6" s="9">
         <v>3.6459999999999999E-2</v>
       </c>
-      <c r="AL6" s="10">
+      <c r="AL6" s="9">
         <v>3.6700000000000003E-2</v>
       </c>
-      <c r="AM6" s="10">
+      <c r="AM6" s="9">
         <v>2.896E-2</v>
       </c>
-      <c r="AN6" s="10">
+      <c r="AN6" s="9">
         <v>2.7179999999999999E-2</v>
       </c>
-      <c r="AO6" s="10">
+      <c r="AO6" s="9">
         <v>2.1539999999999997E-2</v>
       </c>
-      <c r="AP6" s="30"/>
+      <c r="AP6" s="33"/>
       <c r="AQ6" s="3">
         <v>1</v>
       </c>
-      <c r="AR6" s="36"/>
-      <c r="AS6" s="14">
+      <c r="AR6" s="39"/>
+      <c r="AS6" s="13">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="AT6" s="14">
+      <c r="AT6" s="13">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="AU6" s="14">
+      <c r="AU6" s="13">
         <v>2.52E-2</v>
       </c>
-      <c r="AV6" s="33"/>
-      <c r="AW6" s="10">
+      <c r="AV6" s="36"/>
+      <c r="AW6" s="9">
         <v>8.2400000000000008E-3</v>
       </c>
-      <c r="AX6" s="10">
+      <c r="AX6" s="9">
         <v>8.94E-3</v>
       </c>
-      <c r="AY6" s="10">
+      <c r="AY6" s="9">
         <v>8.7600000000000004E-3</v>
       </c>
-      <c r="AZ6" s="10">
+      <c r="AZ6" s="9">
         <v>9.1599999999999997E-3</v>
       </c>
-      <c r="BA6" s="10">
+      <c r="BA6" s="9">
         <v>8.6E-3</v>
       </c>
-      <c r="BB6" s="33"/>
-      <c r="BC6" s="10">
+      <c r="BB6" s="36"/>
+      <c r="BC6" s="9">
         <v>4.2320000000000003E-2</v>
       </c>
-      <c r="BD6" s="10">
+      <c r="BD6" s="9">
         <v>5.4820000000000001E-2</v>
       </c>
-      <c r="BE6" s="10">
+      <c r="BE6" s="9">
         <v>4.6240000000000003E-2</v>
       </c>
-      <c r="BF6" s="10">
+      <c r="BF6" s="9">
         <v>5.2519999999999997E-2</v>
       </c>
-      <c r="BG6" s="10">
+      <c r="BG6" s="9">
         <v>4.9080000000000006E-2</v>
       </c>
-      <c r="BH6" s="33"/>
+      <c r="BH6" s="36"/>
       <c r="BI6" s="1">
         <v>3.6720000000000003E-2</v>
       </c>
@@ -2094,14 +2524,81 @@
         <v>3.9800000000000002E-2</v>
       </c>
       <c r="BN6" s="27"/>
-      <c r="BO6" s="10">
+      <c r="BO6" s="9">
+        <v>3.6459999999999999E-2</v>
+      </c>
+      <c r="BP6" s="9">
+        <v>4.2380000000000001E-2</v>
+      </c>
+      <c r="BQ6" s="1">
+        <v>3.6720000000000003E-2</v>
+      </c>
+      <c r="BR6" s="9">
+        <v>4.2320000000000003E-2</v>
+      </c>
+      <c r="BS6" s="30"/>
+      <c r="BT6" s="9">
         <v>8.7236000000000008E-2</v>
       </c>
-      <c r="BP6" s="10">
+      <c r="BU6" s="9">
         <v>8.7236000000000008E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BV6" s="9">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="BW6" s="9">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="BX6" s="9">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="BY6" s="9">
+        <v>2.52E-2</v>
+      </c>
+      <c r="BZ6" s="9">
+        <v>2.52E-2</v>
+      </c>
+      <c r="CA6" s="9">
+        <v>2.52E-2</v>
+      </c>
+      <c r="CB6" s="9">
+        <v>3.8399999999999997E-2</v>
+      </c>
+      <c r="CC6" s="9">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="CD6" s="9">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="CE6" s="9">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="CF6" s="9">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="CG6" s="9">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="CH6" s="9">
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="CI6" s="9">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="CJ6" s="9">
+        <v>9.7000000000000003E-3</v>
+      </c>
+      <c r="CK6" s="9">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="CL6" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="CM6" s="9">
+        <v>9.4000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2118,10 +2615,10 @@
       <c r="F7" s="3">
         <v>5</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="21">
         <v>2</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <v>1</v>
       </c>
       <c r="I7" s="3">
@@ -2151,21 +2648,21 @@
       <c r="Q7" s="1">
         <v>1</v>
       </c>
-      <c r="R7" s="30"/>
-      <c r="S7" s="12">
+      <c r="R7" s="33"/>
+      <c r="S7" s="11">
         <v>2</v>
       </c>
-      <c r="T7" s="30"/>
-      <c r="U7" s="15">
+      <c r="T7" s="33"/>
+      <c r="U7" s="14">
         <v>4.7233333333333329E-2</v>
       </c>
-      <c r="V7" s="16">
+      <c r="V7" s="15">
         <v>8.2599999999999993E-2</v>
       </c>
-      <c r="W7" s="16">
+      <c r="W7" s="15">
         <v>7.7299999999999994E-2</v>
       </c>
-      <c r="X7" s="33"/>
+      <c r="X7" s="36"/>
       <c r="Y7" s="1">
         <v>3.1020000000000002E-2</v>
       </c>
@@ -2181,7 +2678,7 @@
       <c r="AC7" s="1">
         <v>3.9740000000000004E-2</v>
       </c>
-      <c r="AD7" s="33"/>
+      <c r="AD7" s="36"/>
       <c r="AE7" s="1">
         <v>8.8140000000000024E-2</v>
       </c>
@@ -2197,37 +2694,37 @@
       <c r="AI7" s="1">
         <v>8.6399999999999991E-2</v>
       </c>
-      <c r="AJ7" s="33"/>
-      <c r="AK7" s="10">
+      <c r="AJ7" s="36"/>
+      <c r="AK7" s="9">
         <v>7.4840000000000004E-2</v>
       </c>
-      <c r="AL7" s="10">
+      <c r="AL7" s="9">
         <v>8.6240000000000011E-2</v>
       </c>
-      <c r="AM7" s="10">
+      <c r="AM7" s="9">
         <v>7.2639999999999996E-2</v>
       </c>
-      <c r="AN7" s="10">
+      <c r="AN7" s="9">
         <v>7.2959999999999997E-2</v>
       </c>
-      <c r="AO7" s="10">
+      <c r="AO7" s="9">
         <v>5.4647999999999995E-2</v>
       </c>
-      <c r="AP7" s="30"/>
+      <c r="AP7" s="33"/>
       <c r="AQ7" s="3">
         <v>4</v>
       </c>
-      <c r="AR7" s="36"/>
-      <c r="AS7" s="15">
+      <c r="AR7" s="39"/>
+      <c r="AS7" s="14">
         <v>6.6233333333333352E-2</v>
       </c>
-      <c r="AT7" s="16">
+      <c r="AT7" s="15">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="AU7" s="16">
+      <c r="AU7" s="15">
         <v>8.8700000000000001E-2</v>
       </c>
-      <c r="AV7" s="33"/>
+      <c r="AV7" s="36"/>
       <c r="AW7" s="1">
         <v>6.4219999999999999E-2</v>
       </c>
@@ -2243,7 +2740,7 @@
       <c r="BA7" s="1">
         <v>4.82E-2</v>
       </c>
-      <c r="BB7" s="33"/>
+      <c r="BB7" s="36"/>
       <c r="BC7" s="1">
         <v>5.3959999999999994E-2</v>
       </c>
@@ -2259,7 +2756,7 @@
       <c r="BG7" s="1">
         <v>5.1519999999999996E-2</v>
       </c>
-      <c r="BH7" s="33"/>
+      <c r="BH7" s="36"/>
       <c r="BI7" s="1">
         <v>0.14045999999999997</v>
       </c>
@@ -2276,14 +2773,81 @@
         <v>0.13346</v>
       </c>
       <c r="BN7" s="27"/>
-      <c r="BO7" s="10">
+      <c r="BO7" s="9">
+        <v>7.4840000000000004E-2</v>
+      </c>
+      <c r="BP7" s="1">
+        <v>8.8140000000000024E-2</v>
+      </c>
+      <c r="BQ7" s="1">
+        <v>0.14045999999999997</v>
+      </c>
+      <c r="BR7" s="1">
+        <v>5.3959999999999994E-2</v>
+      </c>
+      <c r="BS7" s="30"/>
+      <c r="BT7" s="9">
         <v>0.11273999999999999</v>
       </c>
-      <c r="BP7" s="10">
+      <c r="BU7" s="9">
         <v>0.11273999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BV7" s="9">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="BW7" s="9">
+        <v>8.6699999999999999E-2</v>
+      </c>
+      <c r="BX7" s="9">
+        <v>7.2700000000000001E-2</v>
+      </c>
+      <c r="BY7" s="9">
+        <v>7.8E-2</v>
+      </c>
+      <c r="BZ7" s="9">
+        <v>8.8099999999999998E-2</v>
+      </c>
+      <c r="CA7" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="CB7" s="9">
+        <v>9.2299999999999993E-2</v>
+      </c>
+      <c r="CC7" s="9">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="CD7" s="9">
+        <v>7.2300000000000003E-2</v>
+      </c>
+      <c r="CE7" s="9">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="CF7" s="9">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="CG7" s="9">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="CH7" s="9">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="CI7" s="9">
+        <v>4.2200000000000001E-2</v>
+      </c>
+      <c r="CJ7" s="9">
+        <v>5.79E-2</v>
+      </c>
+      <c r="CK7" s="9">
+        <v>5.6300000000000003E-2</v>
+      </c>
+      <c r="CL7" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="CM7" s="9">
+        <v>7.2400000000000006E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2300,10 +2864,10 @@
       <c r="F8" s="3">
         <v>2</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="21">
         <v>5</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="21">
         <v>1</v>
       </c>
       <c r="I8" s="3">
@@ -2333,21 +2897,21 @@
       <c r="Q8" s="1">
         <v>15</v>
       </c>
-      <c r="R8" s="30"/>
-      <c r="S8" s="12">
+      <c r="R8" s="33"/>
+      <c r="S8" s="11">
         <v>0</v>
       </c>
-      <c r="T8" s="30"/>
-      <c r="U8" s="17">
+      <c r="T8" s="33"/>
+      <c r="U8" s="16">
         <v>1.0666666666666666E-2</v>
       </c>
-      <c r="V8" s="17">
+      <c r="V8" s="16">
         <v>2.9666666666666664E-2</v>
       </c>
-      <c r="W8" s="17">
+      <c r="W8" s="16">
         <v>8.8133333333333341E-2</v>
       </c>
-      <c r="X8" s="33"/>
+      <c r="X8" s="36"/>
       <c r="Y8" s="1">
         <v>1.9619999999999999E-2</v>
       </c>
@@ -2363,7 +2927,7 @@
       <c r="AC8" s="1">
         <v>1.8180000000000002E-2</v>
       </c>
-      <c r="AD8" s="33"/>
+      <c r="AD8" s="36"/>
       <c r="AE8" s="1">
         <v>6.8080000000000002E-2</v>
       </c>
@@ -2379,7 +2943,7 @@
       <c r="AI8" s="1">
         <v>5.9880000000000003E-2</v>
       </c>
-      <c r="AJ8" s="33"/>
+      <c r="AJ8" s="36"/>
       <c r="AK8" s="1">
         <v>0.13230000000000003</v>
       </c>
@@ -2395,21 +2959,21 @@
       <c r="AO8" s="1">
         <v>0.11194</v>
       </c>
-      <c r="AP8" s="30"/>
+      <c r="AP8" s="33"/>
       <c r="AQ8" s="3">
         <v>2</v>
       </c>
-      <c r="AR8" s="36"/>
-      <c r="AS8" s="15">
+      <c r="AR8" s="39"/>
+      <c r="AS8" s="14">
         <v>1.8866666666666667E-2</v>
       </c>
-      <c r="AT8" s="15">
+      <c r="AT8" s="14">
         <v>6.5266666666666667E-2</v>
       </c>
-      <c r="AU8" s="15">
+      <c r="AU8" s="14">
         <v>8.2966666666666675E-2</v>
       </c>
-      <c r="AV8" s="33"/>
+      <c r="AV8" s="36"/>
       <c r="AW8" s="1">
         <v>2.7460000000000002E-2</v>
       </c>
@@ -2425,7 +2989,7 @@
       <c r="BA8" s="1">
         <v>2.2960000000000001E-2</v>
       </c>
-      <c r="BB8" s="33"/>
+      <c r="BB8" s="36"/>
       <c r="BC8" s="1">
         <v>8.7459999999999996E-2</v>
       </c>
@@ -2441,7 +3005,7 @@
       <c r="BG8" s="1">
         <v>0.22664000000000001</v>
       </c>
-      <c r="BH8" s="33"/>
+      <c r="BH8" s="36"/>
       <c r="BI8" s="1">
         <v>0.13022</v>
       </c>
@@ -2458,14 +3022,81 @@
         <v>0.12172000000000001</v>
       </c>
       <c r="BN8" s="27"/>
-      <c r="BO8" s="10">
+      <c r="BO8" s="1">
+        <v>0.13230000000000003</v>
+      </c>
+      <c r="BP8" s="1">
+        <v>6.8080000000000002E-2</v>
+      </c>
+      <c r="BQ8" s="1">
+        <v>0.13022</v>
+      </c>
+      <c r="BR8" s="1">
+        <v>8.7459999999999996E-2</v>
+      </c>
+      <c r="BS8" s="30"/>
+      <c r="BT8" s="9">
         <v>6.3631999999999994E-2</v>
       </c>
-      <c r="BP8" s="10">
+      <c r="BU8" s="9">
         <v>6.3631999999999994E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BV8" s="9">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="BW8" s="9">
+        <v>0.1205</v>
+      </c>
+      <c r="BX8" s="9">
+        <v>7.2900000000000006E-2</v>
+      </c>
+      <c r="BY8" s="9">
+        <v>7.8E-2</v>
+      </c>
+      <c r="BZ8" s="9">
+        <v>7.9100000000000004E-2</v>
+      </c>
+      <c r="CA8" s="9">
+        <v>9.1800000000000007E-2</v>
+      </c>
+      <c r="CB8" s="9">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="CC8" s="9">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="CD8" s="9">
+        <v>2.2700000000000001E-2</v>
+      </c>
+      <c r="CE8" s="9">
+        <v>9.0399999999999994E-2</v>
+      </c>
+      <c r="CF8" s="9">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="CG8" s="9">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="CH8" s="9">
+        <v>1.24E-2</v>
+      </c>
+      <c r="CI8" s="9">
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="CJ8" s="9">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="CK8" s="9">
+        <v>1.17E-2</v>
+      </c>
+      <c r="CL8" s="9">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="CM8" s="9">
+        <v>2.46E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2482,10 +3113,10 @@
       <c r="F9" s="3">
         <v>1</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="21">
         <v>3</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="21">
         <v>2</v>
       </c>
       <c r="I9" s="3">
@@ -2515,21 +3146,21 @@
       <c r="Q9" s="1">
         <v>0</v>
       </c>
-      <c r="R9" s="30"/>
-      <c r="S9" s="12">
+      <c r="R9" s="33"/>
+      <c r="S9" s="11">
         <v>3</v>
       </c>
-      <c r="T9" s="30"/>
-      <c r="U9" s="15">
+      <c r="T9" s="33"/>
+      <c r="U9" s="14">
         <v>4.0599999999999997E-2</v>
       </c>
-      <c r="V9" s="15">
+      <c r="V9" s="14">
         <v>2.6333333333333334E-2</v>
       </c>
-      <c r="W9" s="15">
+      <c r="W9" s="14">
         <v>3.8399999999999997E-2</v>
       </c>
-      <c r="X9" s="33"/>
+      <c r="X9" s="36"/>
       <c r="Y9" s="1">
         <v>2.776E-2</v>
       </c>
@@ -2545,7 +3176,7 @@
       <c r="AC9" s="1">
         <v>2.776E-2</v>
       </c>
-      <c r="AD9" s="33"/>
+      <c r="AD9" s="36"/>
       <c r="AE9" s="1">
         <v>2.4E-2</v>
       </c>
@@ -2561,37 +3192,37 @@
       <c r="AI9" s="1">
         <v>2.0639999999999999E-2</v>
       </c>
-      <c r="AJ9" s="33"/>
-      <c r="AK9" s="10">
+      <c r="AJ9" s="36"/>
+      <c r="AK9" s="9">
         <v>3.6420000000000001E-2</v>
       </c>
-      <c r="AL9" s="10">
+      <c r="AL9" s="9">
         <v>3.1E-2</v>
       </c>
-      <c r="AM9" s="10">
+      <c r="AM9" s="9">
         <v>2.7979999999999998E-2</v>
       </c>
-      <c r="AN9" s="10">
+      <c r="AN9" s="9">
         <v>2.6040000000000001E-2</v>
       </c>
-      <c r="AO9" s="10">
+      <c r="AO9" s="9">
         <v>2.9499999999999998E-2</v>
       </c>
-      <c r="AP9" s="30"/>
+      <c r="AP9" s="33"/>
       <c r="AQ9" s="3">
         <v>3</v>
       </c>
-      <c r="AR9" s="36"/>
-      <c r="AS9" s="15">
+      <c r="AR9" s="39"/>
+      <c r="AS9" s="14">
         <v>2.7633333333333333E-2</v>
       </c>
-      <c r="AT9" s="15">
+      <c r="AT9" s="14">
         <v>2.1666666666666667E-2</v>
       </c>
-      <c r="AU9" s="15">
+      <c r="AU9" s="14">
         <v>5.7666666666666665E-2</v>
       </c>
-      <c r="AV9" s="33"/>
+      <c r="AV9" s="36"/>
       <c r="AW9" s="1">
         <v>2.7320000000000001E-2</v>
       </c>
@@ -2607,7 +3238,7 @@
       <c r="BA9" s="1">
         <v>2.1700000000000004E-2</v>
       </c>
-      <c r="BB9" s="33"/>
+      <c r="BB9" s="36"/>
       <c r="BC9" s="1">
         <v>2.4320000000000001E-2</v>
       </c>
@@ -2623,7 +3254,7 @@
       <c r="BG9" s="1">
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="BH9" s="33"/>
+      <c r="BH9" s="36"/>
       <c r="BI9" s="1">
         <v>6.0899999999999996E-2</v>
       </c>
@@ -2640,14 +3271,81 @@
         <v>4.7540000000000006E-2</v>
       </c>
       <c r="BN9" s="27"/>
-      <c r="BO9" s="10">
+      <c r="BO9" s="9">
+        <v>3.6420000000000001E-2</v>
+      </c>
+      <c r="BP9" s="1">
+        <v>2.4E-2</v>
+      </c>
+      <c r="BQ9" s="1">
+        <v>6.0899999999999996E-2</v>
+      </c>
+      <c r="BR9" s="1">
+        <v>2.4320000000000001E-2</v>
+      </c>
+      <c r="BS9" s="30"/>
+      <c r="BT9" s="9">
         <v>0.33338799999999996</v>
       </c>
-      <c r="BP9" s="10">
+      <c r="BU9" s="9">
         <v>0.32975600000000005</v>
       </c>
-    </row>
-    <row r="10" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BV9" s="9">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="BW9" s="9">
+        <v>4.5900000000000003E-2</v>
+      </c>
+      <c r="BX9" s="9">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="BY9" s="9">
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="BZ9" s="9">
+        <v>5.5800000000000002E-2</v>
+      </c>
+      <c r="CA9" s="9">
+        <v>5.96E-2</v>
+      </c>
+      <c r="CB9" s="9">
+        <v>2.76E-2</v>
+      </c>
+      <c r="CC9" s="9">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="CD9" s="9">
+        <v>2.46E-2</v>
+      </c>
+      <c r="CE9" s="9">
+        <v>2.29E-2</v>
+      </c>
+      <c r="CF9" s="9">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="CG9" s="9">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="CH9" s="9">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="CI9" s="9">
+        <v>4.7600000000000003E-2</v>
+      </c>
+      <c r="CJ9" s="9">
+        <v>3.4799999999999998E-2</v>
+      </c>
+      <c r="CK9" s="9">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="CL9" s="9">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="CM9" s="9">
+        <v>2.1399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2664,10 +3362,10 @@
       <c r="F10" s="3">
         <v>6</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="21">
         <v>6</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="21">
         <v>1</v>
       </c>
       <c r="I10" s="3">
@@ -2697,21 +3395,21 @@
       <c r="Q10" s="1">
         <v>12</v>
       </c>
-      <c r="R10" s="30"/>
-      <c r="S10" s="12">
+      <c r="R10" s="33"/>
+      <c r="S10" s="11">
         <v>3</v>
       </c>
-      <c r="T10" s="30"/>
-      <c r="U10" s="15">
+      <c r="T10" s="33"/>
+      <c r="U10" s="14">
         <v>3.9633333333333333E-2</v>
       </c>
-      <c r="V10" s="16">
+      <c r="V10" s="15">
         <v>8.1299999999999997E-2</v>
       </c>
-      <c r="W10" s="15">
+      <c r="W10" s="14">
         <v>3.0133333333333335E-2</v>
       </c>
-      <c r="X10" s="33"/>
+      <c r="X10" s="36"/>
       <c r="Y10" s="1">
         <v>3.474E-2</v>
       </c>
@@ -2727,7 +3425,7 @@
       <c r="AC10" s="1">
         <v>2.7499999999999997E-2</v>
       </c>
-      <c r="AD10" s="33"/>
+      <c r="AD10" s="36"/>
       <c r="AE10" s="1">
         <v>0.11834</v>
       </c>
@@ -2743,37 +3441,37 @@
       <c r="AI10" s="1">
         <v>0.12718000000000002</v>
       </c>
-      <c r="AJ10" s="33"/>
-      <c r="AK10" s="10">
+      <c r="AJ10" s="36"/>
+      <c r="AK10" s="9">
         <v>3.7859999999999998E-2</v>
       </c>
-      <c r="AL10" s="10">
+      <c r="AL10" s="9">
         <v>3.2439999999999997E-2</v>
       </c>
-      <c r="AM10" s="10">
+      <c r="AM10" s="9">
         <v>3.2619999999999996E-2</v>
       </c>
-      <c r="AN10" s="10">
+      <c r="AN10" s="9">
         <v>3.5240000000000007E-2</v>
       </c>
-      <c r="AO10" s="10">
+      <c r="AO10" s="9">
         <v>3.4419999999999999E-2</v>
       </c>
-      <c r="AP10" s="30"/>
+      <c r="AP10" s="33"/>
       <c r="AQ10" s="3">
         <v>0</v>
       </c>
-      <c r="AR10" s="36"/>
-      <c r="AS10" s="15">
+      <c r="AR10" s="39"/>
+      <c r="AS10" s="14">
         <v>4.5500000000000006E-2</v>
       </c>
-      <c r="AT10" s="16">
+      <c r="AT10" s="15">
         <v>0.17449999999999999</v>
       </c>
-      <c r="AU10" s="16">
+      <c r="AU10" s="15">
         <v>5.4400000000000004E-2</v>
       </c>
-      <c r="AV10" s="33"/>
+      <c r="AV10" s="36"/>
       <c r="AW10" s="1">
         <v>3.1619999999999995E-2</v>
       </c>
@@ -2789,7 +3487,7 @@
       <c r="BA10" s="1">
         <v>2.5479999999999996E-2</v>
       </c>
-      <c r="BB10" s="33"/>
+      <c r="BB10" s="36"/>
       <c r="BC10" s="1">
         <v>0.22295999999999999</v>
       </c>
@@ -2805,7 +3503,7 @@
       <c r="BG10" s="1">
         <v>0.19668000000000002</v>
       </c>
-      <c r="BH10" s="33"/>
+      <c r="BH10" s="36"/>
       <c r="BI10" s="1">
         <v>6.966E-2</v>
       </c>
@@ -2822,14 +3520,81 @@
         <v>6.9040000000000004E-2</v>
       </c>
       <c r="BN10" s="27"/>
-      <c r="BO10" s="10">
+      <c r="BO10" s="9">
+        <v>3.7859999999999998E-2</v>
+      </c>
+      <c r="BP10" s="1">
+        <v>0.11834</v>
+      </c>
+      <c r="BQ10" s="1">
+        <v>6.966E-2</v>
+      </c>
+      <c r="BR10" s="1">
+        <v>0.22295999999999999</v>
+      </c>
+      <c r="BS10" s="30"/>
+      <c r="BT10" s="9">
         <v>8.4360000000000004E-2</v>
       </c>
-      <c r="BP10" s="10">
+      <c r="BU10" s="9">
         <v>8.4360000000000004E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BV10" s="9">
+        <v>3.15E-2</v>
+      </c>
+      <c r="BW10" s="9">
+        <v>3.32E-2</v>
+      </c>
+      <c r="BX10" s="9">
+        <v>2.5700000000000001E-2</v>
+      </c>
+      <c r="BY10" s="9">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="BZ10" s="9">
+        <v>6.0900000000000003E-2</v>
+      </c>
+      <c r="CA10" s="9">
+        <v>5.57E-2</v>
+      </c>
+      <c r="CB10" s="9">
+        <v>7.0599999999999996E-2</v>
+      </c>
+      <c r="CC10" s="9">
+        <v>9.9400000000000002E-2</v>
+      </c>
+      <c r="CD10" s="9">
+        <v>7.3899999999999993E-2</v>
+      </c>
+      <c r="CE10" s="9">
+        <v>0.19570000000000001</v>
+      </c>
+      <c r="CF10" s="9">
+        <v>0.15359999999999999</v>
+      </c>
+      <c r="CG10" s="9">
+        <v>0.17419999999999999</v>
+      </c>
+      <c r="CH10" s="9">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="CI10" s="9">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="CJ10" s="9">
+        <v>4.3700000000000003E-2</v>
+      </c>
+      <c r="CK10" s="9">
+        <v>3.0599999999999999E-2</v>
+      </c>
+      <c r="CL10" s="9">
+        <v>5.57E-2</v>
+      </c>
+      <c r="CM10" s="9">
+        <v>5.0200000000000002E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2846,10 +3611,10 @@
       <c r="F11" s="3">
         <v>2</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="21">
         <v>5</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="21">
         <v>1</v>
       </c>
       <c r="I11" s="3">
@@ -2879,21 +3644,21 @@
       <c r="Q11" s="1">
         <v>8</v>
       </c>
-      <c r="R11" s="30"/>
-      <c r="S11" s="12">
+      <c r="R11" s="33"/>
+      <c r="S11" s="11">
         <v>2</v>
       </c>
-      <c r="T11" s="30"/>
-      <c r="U11" s="15">
+      <c r="T11" s="33"/>
+      <c r="U11" s="14">
         <v>1.2233333333333332E-2</v>
       </c>
-      <c r="V11" s="15">
+      <c r="V11" s="14">
         <v>4.5866666666666667E-2</v>
       </c>
-      <c r="W11" s="15">
+      <c r="W11" s="14">
         <v>3.7233333333333334E-2</v>
       </c>
-      <c r="X11" s="33"/>
+      <c r="X11" s="36"/>
       <c r="Y11" s="1">
         <v>1.4660000000000001E-2</v>
       </c>
@@ -2909,7 +3674,7 @@
       <c r="AC11" s="1">
         <v>1.0960000000000001E-2</v>
       </c>
-      <c r="AD11" s="33"/>
+      <c r="AD11" s="36"/>
       <c r="AE11" s="1">
         <v>5.4079999999999996E-2</v>
       </c>
@@ -2925,37 +3690,37 @@
       <c r="AI11" s="1">
         <v>4.8420000000000005E-2</v>
       </c>
-      <c r="AJ11" s="33"/>
-      <c r="AK11" s="10">
+      <c r="AJ11" s="36"/>
+      <c r="AK11" s="9">
         <v>3.5099999999999999E-2</v>
       </c>
-      <c r="AL11" s="10">
+      <c r="AL11" s="9">
         <v>3.6159999999999998E-2</v>
       </c>
-      <c r="AM11" s="10">
+      <c r="AM11" s="9">
         <v>3.6240000000000001E-2</v>
       </c>
-      <c r="AN11" s="10">
+      <c r="AN11" s="9">
         <v>3.4820000000000004E-2</v>
       </c>
-      <c r="AO11" s="10">
+      <c r="AO11" s="9">
         <v>3.6059999999999995E-2</v>
       </c>
-      <c r="AP11" s="30"/>
+      <c r="AP11" s="33"/>
       <c r="AQ11" s="3">
         <v>2</v>
       </c>
-      <c r="AR11" s="36"/>
-      <c r="AS11" s="15">
+      <c r="AR11" s="39"/>
+      <c r="AS11" s="14">
         <v>2.3199999999999998E-2</v>
       </c>
-      <c r="AT11" s="15">
+      <c r="AT11" s="14">
         <v>4.5566666666666665E-2</v>
       </c>
-      <c r="AU11" s="15">
+      <c r="AU11" s="14">
         <v>2.6733333333333331E-2</v>
       </c>
-      <c r="AV11" s="33"/>
+      <c r="AV11" s="36"/>
       <c r="AW11" s="1">
         <v>2.666E-2</v>
       </c>
@@ -2971,7 +3736,7 @@
       <c r="BA11" s="1">
         <v>9.1300000000000006E-2</v>
       </c>
-      <c r="BB11" s="33"/>
+      <c r="BB11" s="36"/>
       <c r="BC11" s="1">
         <v>6.1679999999999999E-2</v>
       </c>
@@ -2987,7 +3752,7 @@
       <c r="BG11" s="1">
         <v>6.0000000000000012E-2</v>
       </c>
-      <c r="BH11" s="33"/>
+      <c r="BH11" s="36"/>
       <c r="BI11" s="1">
         <v>3.304E-2</v>
       </c>
@@ -3004,14 +3769,81 @@
         <v>3.798E-2</v>
       </c>
       <c r="BN11" s="27"/>
-      <c r="BO11" s="10">
+      <c r="BO11" s="9">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="BP11" s="1">
+        <v>5.4079999999999996E-2</v>
+      </c>
+      <c r="BQ11" s="1">
+        <v>3.304E-2</v>
+      </c>
+      <c r="BR11" s="1">
+        <v>6.1679999999999999E-2</v>
+      </c>
+      <c r="BS11" s="30"/>
+      <c r="BT11" s="9">
         <v>9.8012000000000002E-2</v>
       </c>
-      <c r="BP11" s="10">
+      <c r="BU11" s="9">
         <v>9.8012000000000002E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BV11" s="9">
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="BW11" s="9">
+        <v>3.8800000000000001E-2</v>
+      </c>
+      <c r="BX11" s="9">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="BY11" s="9">
+        <v>2.93E-2</v>
+      </c>
+      <c r="BZ11" s="9">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="CA11" s="9">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="CB11" s="9">
+        <v>4.4600000000000001E-2</v>
+      </c>
+      <c r="CC11" s="9">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="CD11" s="9">
+        <v>5.3100000000000001E-2</v>
+      </c>
+      <c r="CE11" s="9">
+        <v>4.7E-2</v>
+      </c>
+      <c r="CF11" s="9">
+        <v>5.2900000000000003E-2</v>
+      </c>
+      <c r="CG11" s="9">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="CH11" s="9">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="CI11" s="9">
+        <v>1.29E-2</v>
+      </c>
+      <c r="CJ11" s="9">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="CK11" s="9">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="CL11" s="9">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="CM11" s="9">
+        <v>1.03E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -3028,10 +3860,10 @@
       <c r="F12" s="3">
         <v>3</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="21">
         <v>2</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="21">
         <v>2</v>
       </c>
       <c r="I12" s="3">
@@ -3061,21 +3893,21 @@
       <c r="Q12" s="1">
         <v>8</v>
       </c>
-      <c r="R12" s="30"/>
-      <c r="S12" s="12">
+      <c r="R12" s="33"/>
+      <c r="S12" s="11">
         <v>3</v>
       </c>
-      <c r="T12" s="30"/>
-      <c r="U12" s="15">
+      <c r="T12" s="33"/>
+      <c r="U12" s="14">
         <v>1.9566666666666666E-2</v>
       </c>
-      <c r="V12" s="16">
+      <c r="V12" s="15">
         <v>9.1399999999999995E-2</v>
       </c>
-      <c r="W12" s="15">
+      <c r="W12" s="14">
         <v>0.11086666666666667</v>
       </c>
-      <c r="X12" s="33"/>
+      <c r="X12" s="36"/>
       <c r="Y12" s="1">
         <v>1.0960000000000001E-2</v>
       </c>
@@ -3091,7 +3923,7 @@
       <c r="AC12" s="1">
         <v>1.01E-2</v>
       </c>
-      <c r="AD12" s="33"/>
+      <c r="AD12" s="36"/>
       <c r="AE12" s="1">
         <v>7.9219999999999999E-2</v>
       </c>
@@ -3107,7 +3939,7 @@
       <c r="AI12" s="1">
         <v>6.3339999999999994E-2</v>
       </c>
-      <c r="AJ12" s="33"/>
+      <c r="AJ12" s="36"/>
       <c r="AK12" s="1">
         <v>0.10673999999999999</v>
       </c>
@@ -3123,21 +3955,21 @@
       <c r="AO12" s="1">
         <v>0.10485999999999999</v>
       </c>
-      <c r="AP12" s="30"/>
+      <c r="AP12" s="33"/>
       <c r="AQ12" s="3">
         <v>3</v>
       </c>
-      <c r="AR12" s="36"/>
-      <c r="AS12" s="15">
+      <c r="AR12" s="39"/>
+      <c r="AS12" s="14">
         <v>1.4399999999999998E-2</v>
       </c>
-      <c r="AT12" s="15">
+      <c r="AT12" s="14">
         <v>9.219999999999999E-2</v>
       </c>
-      <c r="AU12" s="15">
+      <c r="AU12" s="14">
         <v>9.2466666666666655E-2</v>
       </c>
-      <c r="AV12" s="33"/>
+      <c r="AV12" s="36"/>
       <c r="AW12" s="1">
         <v>1.1680000000000001E-2</v>
       </c>
@@ -3153,7 +3985,7 @@
       <c r="BA12" s="1">
         <v>1.11E-2</v>
       </c>
-      <c r="BB12" s="33"/>
+      <c r="BB12" s="36"/>
       <c r="BC12" s="1">
         <v>9.6320000000000003E-2</v>
       </c>
@@ -3169,7 +4001,7 @@
       <c r="BG12" s="1">
         <v>8.6159999999999987E-2</v>
       </c>
-      <c r="BH12" s="33"/>
+      <c r="BH12" s="36"/>
       <c r="BI12" s="1">
         <v>0.11210000000000001</v>
       </c>
@@ -3186,14 +4018,81 @@
         <v>0.10189999999999999</v>
       </c>
       <c r="BN12" s="27"/>
-      <c r="BO12" s="11">
+      <c r="BO12" s="1">
+        <v>0.10673999999999999</v>
+      </c>
+      <c r="BP12" s="1">
+        <v>7.9219999999999999E-2</v>
+      </c>
+      <c r="BQ12" s="1">
+        <v>0.11210000000000001</v>
+      </c>
+      <c r="BR12" s="1">
+        <v>9.6320000000000003E-2</v>
+      </c>
+      <c r="BS12" s="30"/>
+      <c r="BT12" s="10">
         <v>2.0228000000000003E-2</v>
       </c>
-      <c r="BP12" s="11">
+      <c r="BU12" s="10">
         <v>2.0228000000000003E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BV12" s="9">
+        <v>9.8199999999999996E-2</v>
+      </c>
+      <c r="BW12" s="9">
+        <v>0.13</v>
+      </c>
+      <c r="BX12" s="9">
+        <v>0.10440000000000001</v>
+      </c>
+      <c r="BY12" s="9">
+        <v>8.6199999999999999E-2</v>
+      </c>
+      <c r="BZ12" s="9">
+        <v>0.10780000000000001</v>
+      </c>
+      <c r="CA12" s="9">
+        <v>8.3400000000000002E-2</v>
+      </c>
+      <c r="CB12" s="9">
+        <v>9.0499999999999997E-2</v>
+      </c>
+      <c r="CC12" s="9">
+        <v>8.0799999999999997E-2</v>
+      </c>
+      <c r="CD12" s="9">
+        <v>0.10290000000000001</v>
+      </c>
+      <c r="CE12" s="9">
+        <v>8.9599999999999999E-2</v>
+      </c>
+      <c r="CF12" s="9">
+        <v>0.11119999999999999</v>
+      </c>
+      <c r="CG12" s="9">
+        <v>7.5800000000000006E-2</v>
+      </c>
+      <c r="CH12" s="9">
+        <v>2.24E-2</v>
+      </c>
+      <c r="CI12" s="9">
+        <v>2.3199999999999998E-2</v>
+      </c>
+      <c r="CJ12" s="9">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="CK12" s="9">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="CL12" s="9">
+        <v>1.61E-2</v>
+      </c>
+      <c r="CM12" s="9">
+        <v>8.3999999999999995E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3210,10 +4109,10 @@
       <c r="F13" s="3">
         <v>1</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="21">
         <v>14</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="21">
         <v>2</v>
       </c>
       <c r="I13" s="3">
@@ -3243,21 +4142,21 @@
       <c r="Q13" s="1">
         <v>3</v>
       </c>
-      <c r="R13" s="30"/>
-      <c r="S13" s="12">
+      <c r="R13" s="33"/>
+      <c r="S13" s="11">
         <v>4</v>
       </c>
-      <c r="T13" s="30"/>
-      <c r="U13" s="15">
+      <c r="T13" s="33"/>
+      <c r="U13" s="14">
         <v>6.0366666666666659E-2</v>
       </c>
-      <c r="V13" s="15">
+      <c r="V13" s="14">
         <v>4.816666666666667E-2</v>
       </c>
-      <c r="W13" s="15">
+      <c r="W13" s="14">
         <v>2.8733333333333333E-2</v>
       </c>
-      <c r="X13" s="33"/>
+      <c r="X13" s="36"/>
       <c r="Y13" s="1">
         <v>1.336E-2</v>
       </c>
@@ -3273,7 +4172,7 @@
       <c r="AC13" s="1">
         <v>1.7099999999999997E-2</v>
       </c>
-      <c r="AD13" s="33"/>
+      <c r="AD13" s="36"/>
       <c r="AE13" s="1">
         <v>3.4820000000000004E-2</v>
       </c>
@@ -3289,7 +4188,7 @@
       <c r="AI13" s="1">
         <v>4.0599999999999997E-2</v>
       </c>
-      <c r="AJ13" s="33"/>
+      <c r="AJ13" s="36"/>
       <c r="AK13" s="1">
         <v>1.584E-2</v>
       </c>
@@ -3305,21 +4204,21 @@
       <c r="AO13" s="1">
         <v>1.5559999999999999E-2</v>
       </c>
-      <c r="AP13" s="30"/>
+      <c r="AP13" s="33"/>
       <c r="AQ13" s="3">
         <v>3</v>
       </c>
-      <c r="AR13" s="36"/>
-      <c r="AS13" s="15">
+      <c r="AR13" s="39"/>
+      <c r="AS13" s="14">
         <v>3.4599999999999999E-2</v>
       </c>
-      <c r="AT13" s="16">
+      <c r="AT13" s="15">
         <v>4.9800000000000004E-2</v>
       </c>
-      <c r="AU13" s="16">
+      <c r="AU13" s="15">
         <v>2.92E-2</v>
       </c>
-      <c r="AV13" s="33"/>
+      <c r="AV13" s="36"/>
       <c r="AW13" s="1">
         <v>2.2740000000000003E-2</v>
       </c>
@@ -3335,7 +4234,7 @@
       <c r="BA13" s="1">
         <v>2.7479999999999997E-2</v>
       </c>
-      <c r="BB13" s="33"/>
+      <c r="BB13" s="36"/>
       <c r="BC13" s="1">
         <v>4.8280000000000003E-2</v>
       </c>
@@ -3351,7 +4250,7 @@
       <c r="BG13" s="1">
         <v>5.7179999999999995E-2</v>
       </c>
-      <c r="BH13" s="33"/>
+      <c r="BH13" s="36"/>
       <c r="BI13" s="1">
         <v>3.1300000000000001E-2</v>
       </c>
@@ -3368,195 +4267,329 @@
         <v>3.9660000000000001E-2</v>
       </c>
       <c r="BN13" s="27"/>
-      <c r="BO13" s="10">
+      <c r="BO13" s="1">
+        <v>1.584E-2</v>
+      </c>
+      <c r="BP13" s="1">
+        <v>3.4820000000000004E-2</v>
+      </c>
+      <c r="BQ13" s="1">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="BR13" s="1">
+        <v>4.8280000000000003E-2</v>
+      </c>
+      <c r="BS13" s="30"/>
+      <c r="BT13" s="9">
         <v>1.4036000000000002E-2</v>
       </c>
-      <c r="BP13" s="10">
+      <c r="BU13" s="9">
         <v>1.4036000000000002E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A14" s="23">
+      <c r="BV13" s="9">
+        <v>3.32E-2</v>
+      </c>
+      <c r="BW13" s="9">
+        <v>2.01E-2</v>
+      </c>
+      <c r="BX13" s="9">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BY13" s="9">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="BZ13" s="9">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="CA13" s="9">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="CB13" s="9">
+        <v>4.36E-2</v>
+      </c>
+      <c r="CC13" s="9">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="CD13" s="9">
+        <v>6.5500000000000003E-2</v>
+      </c>
+      <c r="CE13" s="9">
+        <v>5.1700000000000003E-2</v>
+      </c>
+      <c r="CF13" s="9">
+        <v>5.0599999999999999E-2</v>
+      </c>
+      <c r="CG13" s="9">
+        <v>4.7100000000000003E-2</v>
+      </c>
+      <c r="CH13" s="9">
+        <v>3.8300000000000001E-2</v>
+      </c>
+      <c r="CI13" s="9">
+        <v>5.7700000000000001E-2</v>
+      </c>
+      <c r="CJ13" s="9">
+        <v>8.5099999999999995E-2</v>
+      </c>
+      <c r="CK13" s="9">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="CL13" s="9">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="CM13" s="9">
+        <v>4.2700000000000002E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A14" s="22">
         <v>13</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <v>1</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="18">
         <v>55</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="18">
         <v>7</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="18">
         <v>5</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="18">
         <v>1</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="22">
         <v>500</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="18">
         <v>27</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="18">
         <v>170</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="18">
         <v>179</v>
       </c>
-      <c r="M14" s="19">
+      <c r="M14" s="18">
         <v>90</v>
       </c>
-      <c r="N14" s="21">
+      <c r="N14" s="20">
         <v>25</v>
       </c>
-      <c r="O14" s="21">
+      <c r="O14" s="20">
         <v>26</v>
       </c>
-      <c r="P14" s="21">
+      <c r="P14" s="20">
         <v>7</v>
       </c>
-      <c r="Q14" s="21">
+      <c r="Q14" s="20">
         <v>6</v>
       </c>
-      <c r="R14" s="30"/>
-      <c r="S14" s="20">
+      <c r="R14" s="33"/>
+      <c r="S14" s="19">
         <v>3</v>
       </c>
-      <c r="T14" s="30"/>
-      <c r="U14" s="24">
+      <c r="T14" s="33"/>
+      <c r="U14" s="23">
         <v>0.11406666666666666</v>
       </c>
-      <c r="V14" s="24">
+      <c r="V14" s="23">
         <v>5.9333333333333328E-2</v>
       </c>
-      <c r="W14" s="24">
+      <c r="W14" s="23">
         <v>0.14266666666666664</v>
       </c>
-      <c r="X14" s="33"/>
-      <c r="Y14" s="18">
+      <c r="X14" s="36"/>
+      <c r="Y14" s="17">
         <v>0.10018000000000001</v>
       </c>
-      <c r="Z14" s="18">
+      <c r="Z14" s="17">
         <v>9.7559999999999994E-2</v>
       </c>
-      <c r="AA14" s="18">
+      <c r="AA14" s="17">
         <v>7.1720000000000006E-2</v>
       </c>
-      <c r="AB14" s="18">
+      <c r="AB14" s="17">
         <v>7.7520000000000006E-2</v>
       </c>
-      <c r="AC14" s="18">
+      <c r="AC14" s="17">
         <v>6.6640000000000005E-2</v>
       </c>
-      <c r="AD14" s="33"/>
-      <c r="AE14" s="18">
+      <c r="AD14" s="36"/>
+      <c r="AE14" s="17">
         <v>7.9880000000000007E-2</v>
       </c>
-      <c r="AF14" s="18">
+      <c r="AF14" s="17">
         <v>7.0180000000000006E-2</v>
       </c>
-      <c r="AG14" s="18">
+      <c r="AG14" s="17">
         <v>5.4100000000000002E-2</v>
       </c>
-      <c r="AH14" s="18">
+      <c r="AH14" s="17">
         <v>7.0739999999999997E-2</v>
       </c>
-      <c r="AI14" s="18">
+      <c r="AI14" s="17">
         <v>5.528000000000001E-2</v>
       </c>
-      <c r="AJ14" s="33"/>
-      <c r="AK14" s="18">
+      <c r="AJ14" s="36"/>
+      <c r="AK14" s="17">
         <v>0.13911999999999999</v>
       </c>
-      <c r="AL14" s="18">
+      <c r="AL14" s="17">
         <v>0.13950000000000001</v>
       </c>
-      <c r="AM14" s="18">
+      <c r="AM14" s="17">
         <v>0.11346000000000001</v>
       </c>
-      <c r="AN14" s="18">
+      <c r="AN14" s="17">
         <v>0.11588</v>
       </c>
-      <c r="AO14" s="18">
+      <c r="AO14" s="17">
         <v>0.10154000000000001</v>
       </c>
-      <c r="AP14" s="30"/>
-      <c r="AQ14" s="19">
+      <c r="AP14" s="33"/>
+      <c r="AQ14" s="18">
         <v>4</v>
       </c>
-      <c r="AR14" s="36"/>
-      <c r="AS14" s="24">
+      <c r="AR14" s="39"/>
+      <c r="AS14" s="23">
         <v>9.0366666666666665E-2</v>
       </c>
-      <c r="AT14" s="24">
+      <c r="AT14" s="23">
         <v>6.9533333333333336E-2</v>
       </c>
-      <c r="AU14" s="24">
+      <c r="AU14" s="23">
         <v>0.12956666666666669</v>
       </c>
-      <c r="AV14" s="33"/>
-      <c r="AW14" s="18">
+      <c r="AV14" s="36"/>
+      <c r="AW14" s="17">
         <v>0.1038</v>
       </c>
-      <c r="AX14" s="18">
+      <c r="AX14" s="17">
         <v>9.0560000000000002E-2</v>
       </c>
-      <c r="AY14" s="18">
+      <c r="AY14" s="17">
         <v>8.2680000000000003E-2</v>
       </c>
-      <c r="AZ14" s="18">
+      <c r="AZ14" s="17">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="BA14" s="18">
+      <c r="BA14" s="17">
         <v>6.9940000000000002E-2</v>
       </c>
-      <c r="BB14" s="33"/>
-      <c r="BC14" s="18">
+      <c r="BB14" s="36"/>
+      <c r="BC14" s="17">
         <v>9.8580000000000001E-2</v>
       </c>
-      <c r="BD14" s="18">
+      <c r="BD14" s="17">
         <v>7.9740000000000005E-2</v>
       </c>
-      <c r="BE14" s="18">
+      <c r="BE14" s="17">
         <v>7.6780000000000001E-2</v>
       </c>
-      <c r="BF14" s="18">
+      <c r="BF14" s="17">
         <v>8.3599999999999994E-2</v>
       </c>
-      <c r="BG14" s="18">
+      <c r="BG14" s="17">
         <v>7.9820000000000002E-2</v>
       </c>
-      <c r="BH14" s="33"/>
-      <c r="BI14" s="18">
+      <c r="BH14" s="36"/>
+      <c r="BI14" s="17">
         <v>0.15790000000000001</v>
       </c>
-      <c r="BJ14" s="18">
+      <c r="BJ14" s="17">
         <v>0.15690000000000001</v>
       </c>
-      <c r="BK14" s="18">
+      <c r="BK14" s="17">
         <v>0.13533999999999999</v>
       </c>
-      <c r="BL14" s="18">
+      <c r="BL14" s="17">
         <v>0.14294000000000001</v>
       </c>
-      <c r="BM14" s="18">
+      <c r="BM14" s="17">
         <v>0.12074</v>
       </c>
       <c r="BN14" s="27"/>
-      <c r="BO14" s="10">
+      <c r="BO14" s="17">
+        <v>0.13911999999999999</v>
+      </c>
+      <c r="BP14" s="17">
+        <v>7.9880000000000007E-2</v>
+      </c>
+      <c r="BQ14" s="17">
+        <v>0.15790000000000001</v>
+      </c>
+      <c r="BR14" s="17">
+        <v>9.8580000000000001E-2</v>
+      </c>
+      <c r="BS14" s="30"/>
+      <c r="BT14" s="9">
         <v>1.6403999999999998E-2</v>
       </c>
-      <c r="BP14" s="10">
+      <c r="BU14" s="9">
         <v>1.6403999999999998E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:69" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="BV14" s="9">
+        <v>0.13189999999999999</v>
+      </c>
+      <c r="BW14" s="9">
+        <v>0.18</v>
+      </c>
+      <c r="BX14" s="9">
+        <v>0.11609999999999999</v>
+      </c>
+      <c r="BY14" s="9">
+        <v>0.16220000000000001</v>
+      </c>
+      <c r="BZ14" s="9">
+        <v>8.6599999999999996E-2</v>
+      </c>
+      <c r="CA14" s="9">
+        <v>0.1399</v>
+      </c>
+      <c r="CB14" s="9">
+        <v>6.6799999999999998E-2</v>
+      </c>
+      <c r="CC14" s="9">
+        <v>4.58E-2</v>
+      </c>
+      <c r="CD14" s="9">
+        <v>6.54E-2</v>
+      </c>
+      <c r="CE14" s="9">
+        <v>0.1094</v>
+      </c>
+      <c r="CF14" s="9">
+        <v>5.5199999999999999E-2</v>
+      </c>
+      <c r="CG14" s="9">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="CH14" s="9">
+        <v>9.06E-2</v>
+      </c>
+      <c r="CI14" s="9">
+        <v>0.12809999999999999</v>
+      </c>
+      <c r="CJ14" s="9">
+        <v>0.1235</v>
+      </c>
+      <c r="CK14" s="9">
+        <v>0.12189999999999999</v>
+      </c>
+      <c r="CL14" s="9">
+        <v>0.1016</v>
+      </c>
+      <c r="CM14" s="9">
+        <v>4.7600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:91" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -3606,21 +4639,21 @@
       <c r="Q15" s="1">
         <v>20</v>
       </c>
-      <c r="R15" s="30"/>
+      <c r="R15" s="33"/>
       <c r="S15" s="3">
         <v>5</v>
       </c>
-      <c r="T15" s="30"/>
-      <c r="U15" s="15">
+      <c r="T15" s="33"/>
+      <c r="U15" s="14">
         <v>2.6666666666666661E-2</v>
       </c>
-      <c r="V15" s="15">
+      <c r="V15" s="14">
         <v>8.4033333333333335E-2</v>
       </c>
-      <c r="W15" s="15">
+      <c r="W15" s="14">
         <v>0.10723333333333335</v>
       </c>
-      <c r="X15" s="33"/>
+      <c r="X15" s="36"/>
       <c r="Y15" s="1">
         <v>2.5180000000000001E-2</v>
       </c>
@@ -3636,7 +4669,7 @@
       <c r="AC15" s="1">
         <v>2.494E-2</v>
       </c>
-      <c r="AD15" s="33"/>
+      <c r="AD15" s="36"/>
       <c r="AE15" s="1">
         <v>7.986E-2</v>
       </c>
@@ -3652,7 +4685,7 @@
       <c r="AI15" s="1">
         <v>8.0140000000000003E-2</v>
       </c>
-      <c r="AJ15" s="33"/>
+      <c r="AJ15" s="36"/>
       <c r="AK15" s="1">
         <v>0.11762600000000001</v>
       </c>
@@ -3668,21 +4701,21 @@
       <c r="AO15" s="1">
         <v>0.12581999999999999</v>
       </c>
-      <c r="AP15" s="30"/>
+      <c r="AP15" s="33"/>
       <c r="AQ15" s="3">
         <v>5</v>
       </c>
-      <c r="AR15" s="36"/>
-      <c r="AS15" s="15">
+      <c r="AR15" s="39"/>
+      <c r="AS15" s="14">
         <v>2.8733333333333333E-2</v>
       </c>
-      <c r="AT15" s="16">
+      <c r="AT15" s="15">
         <v>7.7799999999999994E-2</v>
       </c>
-      <c r="AU15" s="15">
+      <c r="AU15" s="14">
         <v>0.11516666666666668</v>
       </c>
-      <c r="AV15" s="33"/>
+      <c r="AV15" s="36"/>
       <c r="AW15" s="1">
         <v>2.6739999999999996E-2</v>
       </c>
@@ -3698,7 +4731,7 @@
       <c r="BA15" s="1">
         <v>2.8999999999999998E-2</v>
       </c>
-      <c r="BB15" s="33"/>
+      <c r="BB15" s="36"/>
       <c r="BC15" s="1">
         <v>7.6399999999999996E-2</v>
       </c>
@@ -3714,7 +4747,7 @@
       <c r="BG15" s="1">
         <v>8.5080000000000003E-2</v>
       </c>
-      <c r="BH15" s="33"/>
+      <c r="BH15" s="36"/>
       <c r="BI15" s="1">
         <v>0.14641999999999999</v>
       </c>
@@ -3731,15 +4764,81 @@
         <v>0.13372000000000001</v>
       </c>
       <c r="BN15" s="27"/>
-      <c r="BO15" s="10">
+      <c r="BO15" s="1">
+        <v>0.11762600000000001</v>
+      </c>
+      <c r="BP15" s="1">
+        <v>7.986E-2</v>
+      </c>
+      <c r="BQ15" s="1">
+        <v>0.14641999999999999</v>
+      </c>
+      <c r="BR15" s="1">
+        <v>7.6399999999999996E-2</v>
+      </c>
+      <c r="BS15" s="30"/>
+      <c r="BT15" s="9">
         <v>2.3023999999999996E-2</v>
       </c>
-      <c r="BP15" s="10">
+      <c r="BU15" s="9">
         <v>2.3023999999999996E-2</v>
       </c>
-      <c r="BQ15" s="9"/>
-    </row>
-    <row r="16" spans="1:69" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="BV15" s="9">
+        <v>0.1033</v>
+      </c>
+      <c r="BW15" s="9">
+        <v>0.1087</v>
+      </c>
+      <c r="BX15" s="9">
+        <v>0.10970000000000001</v>
+      </c>
+      <c r="BY15" s="9">
+        <v>0.1348</v>
+      </c>
+      <c r="BZ15" s="9">
+        <v>0.1046</v>
+      </c>
+      <c r="CA15" s="9">
+        <v>0.1061</v>
+      </c>
+      <c r="CB15" s="9">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="CC15" s="9">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="CD15" s="9">
+        <v>9.01E-2</v>
+      </c>
+      <c r="CE15" s="9">
+        <v>9.2399999999999996E-2</v>
+      </c>
+      <c r="CF15" s="9">
+        <v>8.1699999999999995E-2</v>
+      </c>
+      <c r="CG15" s="9">
+        <v>5.9299999999999999E-2</v>
+      </c>
+      <c r="CH15" s="9">
+        <v>2.41E-2</v>
+      </c>
+      <c r="CI15" s="9">
+        <v>3.3399999999999999E-2</v>
+      </c>
+      <c r="CJ15" s="9">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="CK15" s="9">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="CL15" s="9">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="CM15" s="9">
+        <v>2.1299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:91" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -3789,21 +4888,21 @@
       <c r="Q16" s="1">
         <v>11</v>
       </c>
-      <c r="R16" s="30"/>
+      <c r="R16" s="33"/>
       <c r="S16" s="3">
         <v>1</v>
       </c>
-      <c r="T16" s="30"/>
-      <c r="U16" s="15">
+      <c r="T16" s="33"/>
+      <c r="U16" s="14">
         <v>1.0433333333333334E-2</v>
       </c>
-      <c r="V16" s="15">
+      <c r="V16" s="14">
         <v>2.8933333333333328E-2</v>
       </c>
-      <c r="W16" s="15">
+      <c r="W16" s="14">
         <v>1.6233333333333332E-2</v>
       </c>
-      <c r="X16" s="33"/>
+      <c r="X16" s="36"/>
       <c r="Y16" s="1">
         <v>1.3519999999999999E-2</v>
       </c>
@@ -3819,7 +4918,7 @@
       <c r="AC16" s="1">
         <v>1.406E-2</v>
       </c>
-      <c r="AD16" s="33"/>
+      <c r="AD16" s="36"/>
       <c r="AE16" s="1">
         <v>2.9200000000000004E-2</v>
       </c>
@@ -3835,7 +4934,7 @@
       <c r="AI16" s="1">
         <v>2.9839999999999998E-2</v>
       </c>
-      <c r="AJ16" s="33"/>
+      <c r="AJ16" s="36"/>
       <c r="AK16" s="1">
         <v>1.3040000000000001E-2</v>
       </c>
@@ -3851,21 +4950,21 @@
       <c r="AO16" s="1">
         <v>1.1600000000000003E-2</v>
       </c>
-      <c r="AP16" s="30"/>
+      <c r="AP16" s="33"/>
       <c r="AQ16" s="3">
         <v>4</v>
       </c>
-      <c r="AR16" s="36"/>
-      <c r="AS16" s="15">
+      <c r="AR16" s="39"/>
+      <c r="AS16" s="14">
         <v>8.0333333333333333E-3</v>
       </c>
-      <c r="AT16" s="15">
+      <c r="AT16" s="14">
         <v>2.9433333333333329E-2</v>
       </c>
-      <c r="AU16" s="15">
+      <c r="AU16" s="14">
         <v>2.6166666666666668E-2</v>
       </c>
-      <c r="AV16" s="33"/>
+      <c r="AV16" s="36"/>
       <c r="AW16" s="1">
         <v>9.6600000000000002E-3</v>
       </c>
@@ -3881,7 +4980,7 @@
       <c r="BA16" s="1">
         <v>2.5559999999999999E-2</v>
       </c>
-      <c r="BB16" s="33"/>
+      <c r="BB16" s="36"/>
       <c r="BC16" s="1">
         <v>3.1559999999999998E-2</v>
       </c>
@@ -3897,7 +4996,7 @@
       <c r="BG16" s="1">
         <v>3.6339999999999997E-2</v>
       </c>
-      <c r="BH16" s="33"/>
+      <c r="BH16" s="36"/>
       <c r="BI16" s="1">
         <v>3.5180000000000003E-2</v>
       </c>
@@ -3914,15 +5013,81 @@
         <v>2.0459999999999999E-2</v>
       </c>
       <c r="BN16" s="27"/>
-      <c r="BO16" s="10">
+      <c r="BO16" s="1">
+        <v>1.3040000000000001E-2</v>
+      </c>
+      <c r="BP16" s="1">
+        <v>2.9200000000000004E-2</v>
+      </c>
+      <c r="BQ16" s="1">
+        <v>3.5180000000000003E-2</v>
+      </c>
+      <c r="BR16" s="1">
+        <v>3.1559999999999998E-2</v>
+      </c>
+      <c r="BS16" s="30"/>
+      <c r="BT16" s="9">
         <v>8.992E-3</v>
       </c>
-      <c r="BP16" s="10">
+      <c r="BU16" s="9">
         <v>6.5799999999999999E-3</v>
       </c>
-      <c r="BQ16" s="9"/>
-    </row>
-    <row r="17" spans="1:69" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="BV16" s="9">
+        <v>1.18E-2</v>
+      </c>
+      <c r="BW16" s="9">
+        <v>1.47E-2</v>
+      </c>
+      <c r="BX16" s="9">
+        <v>2.2200000000000001E-2</v>
+      </c>
+      <c r="BY16" s="9">
+        <v>2.69E-2</v>
+      </c>
+      <c r="BZ16" s="9">
+        <v>2.63E-2</v>
+      </c>
+      <c r="CA16" s="9">
+        <v>2.53E-2</v>
+      </c>
+      <c r="CB16" s="9">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="CC16" s="9">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="CD16" s="9">
+        <v>2.75E-2</v>
+      </c>
+      <c r="CE16" s="9">
+        <v>2.7300000000000001E-2</v>
+      </c>
+      <c r="CF16" s="9">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="CG16" s="9">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="CH16" s="9">
+        <v>1.12E-2</v>
+      </c>
+      <c r="CI16" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="CJ16" s="9">
+        <v>1.01E-2</v>
+      </c>
+      <c r="CK16" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="CL16" s="9">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="CM16" s="9">
+        <v>8.8999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:91" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -3972,21 +5137,21 @@
       <c r="Q17" s="1">
         <v>18</v>
       </c>
-      <c r="R17" s="30"/>
+      <c r="R17" s="33"/>
       <c r="S17" s="3">
         <v>1</v>
       </c>
-      <c r="T17" s="30"/>
-      <c r="U17" s="13">
+      <c r="T17" s="33"/>
+      <c r="U17" s="12">
         <v>0.15846666666666667</v>
       </c>
-      <c r="V17" s="13">
+      <c r="V17" s="12">
         <v>0.13073333333333334</v>
       </c>
-      <c r="W17" s="13">
+      <c r="W17" s="12">
         <v>0.10156666666666665</v>
       </c>
-      <c r="X17" s="33"/>
+      <c r="X17" s="36"/>
       <c r="Y17" s="1">
         <v>0.12795999999999999</v>
       </c>
@@ -4002,7 +5167,7 @@
       <c r="AC17" s="1">
         <v>0.12486</v>
       </c>
-      <c r="AD17" s="33"/>
+      <c r="AD17" s="36"/>
       <c r="AE17" s="1">
         <v>0.14988000000000001</v>
       </c>
@@ -4018,7 +5183,7 @@
       <c r="AI17" s="1">
         <v>0.12501999999999999</v>
       </c>
-      <c r="AJ17" s="33"/>
+      <c r="AJ17" s="36"/>
       <c r="AK17" s="1">
         <v>0.11799999999999999</v>
       </c>
@@ -4034,21 +5199,21 @@
       <c r="AO17" s="1">
         <v>0.11734</v>
       </c>
-      <c r="AP17" s="30"/>
+      <c r="AP17" s="33"/>
       <c r="AQ17" s="3">
         <v>2</v>
       </c>
-      <c r="AR17" s="36"/>
-      <c r="AS17" s="13">
+      <c r="AR17" s="39"/>
+      <c r="AS17" s="12">
         <v>7.9100000000000004E-2</v>
       </c>
-      <c r="AT17" s="13">
+      <c r="AT17" s="12">
         <v>9.2766666666666664E-2</v>
       </c>
-      <c r="AU17" s="13">
+      <c r="AU17" s="12">
         <v>0.20106666666666664</v>
       </c>
-      <c r="AV17" s="33"/>
+      <c r="AV17" s="36"/>
       <c r="AW17" s="1">
         <v>9.8979999999999999E-2</v>
       </c>
@@ -4064,7 +5229,7 @@
       <c r="BA17" s="1">
         <v>8.7400000000000005E-2</v>
       </c>
-      <c r="BB17" s="33"/>
+      <c r="BB17" s="36"/>
       <c r="BC17" s="1">
         <v>0.12776000000000001</v>
       </c>
@@ -4080,7 +5245,7 @@
       <c r="BG17" s="1">
         <v>0.1192</v>
       </c>
-      <c r="BH17" s="33"/>
+      <c r="BH17" s="36"/>
       <c r="BI17" s="1">
         <v>0.29430000000000001</v>
       </c>
@@ -4097,15 +5262,81 @@
         <v>0.29236000000000006</v>
       </c>
       <c r="BN17" s="27"/>
-      <c r="BO17" s="10">
+      <c r="BO17" s="1">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="BP17" s="1">
+        <v>0.14988000000000001</v>
+      </c>
+      <c r="BQ17" s="1">
+        <v>0.29430000000000001</v>
+      </c>
+      <c r="BR17" s="1">
+        <v>0.12776000000000001</v>
+      </c>
+      <c r="BS17" s="30"/>
+      <c r="BT17" s="9">
         <v>2.2116000000000004E-2</v>
       </c>
-      <c r="BP17" s="10">
+      <c r="BU17" s="9">
         <v>2.2116000000000004E-2</v>
       </c>
-      <c r="BQ17" s="9"/>
-    </row>
-    <row r="18" spans="1:69" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="BV17" s="9">
+        <v>9.4899999999999998E-2</v>
+      </c>
+      <c r="BW17" s="9">
+        <v>0.1123</v>
+      </c>
+      <c r="BX17" s="9">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="BY17" s="9">
+        <v>0.2152</v>
+      </c>
+      <c r="BZ17" s="9">
+        <v>0.18840000000000001</v>
+      </c>
+      <c r="CA17" s="9">
+        <v>0.1996</v>
+      </c>
+      <c r="CB17" s="9">
+        <v>0.1081</v>
+      </c>
+      <c r="CC17" s="9">
+        <v>0.14460000000000001</v>
+      </c>
+      <c r="CD17" s="9">
+        <v>0.13950000000000001</v>
+      </c>
+      <c r="CE17" s="9">
+        <v>0.13320000000000001</v>
+      </c>
+      <c r="CF17" s="9">
+        <v>7.1800000000000003E-2</v>
+      </c>
+      <c r="CG17" s="9">
+        <v>7.3300000000000004E-2</v>
+      </c>
+      <c r="CH17" s="9">
+        <v>0.18759999999999999</v>
+      </c>
+      <c r="CI17" s="9">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="CJ17" s="9">
+        <v>0.14480000000000001</v>
+      </c>
+      <c r="CK17" s="9">
+        <v>6.7500000000000004E-2</v>
+      </c>
+      <c r="CL17" s="9">
+        <v>6.0100000000000001E-2</v>
+      </c>
+      <c r="CM17" s="9">
+        <v>0.10970000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:91" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -4155,21 +5386,21 @@
       <c r="Q18" s="1">
         <v>1</v>
       </c>
-      <c r="R18" s="30"/>
+      <c r="R18" s="33"/>
       <c r="S18" s="3">
         <v>0</v>
       </c>
-      <c r="T18" s="30"/>
-      <c r="U18" s="15">
+      <c r="T18" s="33"/>
+      <c r="U18" s="14">
         <v>1.2366666666666665E-2</v>
       </c>
-      <c r="V18" s="15">
+      <c r="V18" s="14">
         <v>5.4799999999999995E-2</v>
       </c>
-      <c r="W18" s="15">
+      <c r="W18" s="14">
         <v>3.0933333333333337E-2</v>
       </c>
-      <c r="X18" s="33"/>
+      <c r="X18" s="36"/>
       <c r="Y18" s="1">
         <v>1.4540000000000001E-2</v>
       </c>
@@ -4185,7 +5416,7 @@
       <c r="AC18" s="1">
         <v>1.444E-2</v>
       </c>
-      <c r="AD18" s="33"/>
+      <c r="AD18" s="36"/>
       <c r="AE18" s="1">
         <v>4.8980000000000003E-2</v>
       </c>
@@ -4201,7 +5432,7 @@
       <c r="AI18" s="1">
         <v>4.7219999999999998E-2</v>
       </c>
-      <c r="AJ18" s="33"/>
+      <c r="AJ18" s="36"/>
       <c r="AK18" s="1">
         <v>3.6900000000000002E-2</v>
       </c>
@@ -4217,21 +5448,21 @@
       <c r="AO18" s="1">
         <v>2.8339999999999997E-2</v>
       </c>
-      <c r="AP18" s="30"/>
+      <c r="AP18" s="33"/>
       <c r="AQ18" s="3">
         <v>5</v>
       </c>
-      <c r="AR18" s="36"/>
-      <c r="AS18" s="15">
+      <c r="AR18" s="39"/>
+      <c r="AS18" s="14">
         <v>1.5533333333333335E-2</v>
       </c>
-      <c r="AT18" s="15">
+      <c r="AT18" s="14">
         <v>8.0866666666666656E-2</v>
       </c>
-      <c r="AU18" s="15">
+      <c r="AU18" s="14">
         <v>4.0366666666666669E-2</v>
       </c>
-      <c r="AV18" s="33"/>
+      <c r="AV18" s="36"/>
       <c r="AW18" s="1">
         <v>1.3259999999999999E-2</v>
       </c>
@@ -4247,7 +5478,7 @@
       <c r="BA18" s="1">
         <v>1.668E-2</v>
       </c>
-      <c r="BB18" s="33"/>
+      <c r="BB18" s="36"/>
       <c r="BC18" s="1">
         <v>6.9259999999999988E-2</v>
       </c>
@@ -4263,7 +5494,7 @@
       <c r="BG18" s="1">
         <v>7.282000000000001E-2</v>
       </c>
-      <c r="BH18" s="33"/>
+      <c r="BH18" s="36"/>
       <c r="BI18" s="1">
         <v>4.5420000000000002E-2</v>
       </c>
@@ -4280,15 +5511,81 @@
         <v>3.7699999999999997E-2</v>
       </c>
       <c r="BN18" s="27"/>
-      <c r="BO18" s="10">
+      <c r="BO18" s="1">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="BP18" s="1">
+        <v>4.8980000000000003E-2</v>
+      </c>
+      <c r="BQ18" s="1">
+        <v>4.5420000000000002E-2</v>
+      </c>
+      <c r="BR18" s="1">
+        <v>6.9259999999999988E-2</v>
+      </c>
+      <c r="BS18" s="30"/>
+      <c r="BT18" s="9">
         <v>1.6896000000000001E-2</v>
       </c>
-      <c r="BP18" s="10">
+      <c r="BU18" s="9">
         <v>1.6896000000000001E-2</v>
       </c>
-      <c r="BQ18" s="9"/>
-    </row>
-    <row r="19" spans="1:69" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="BV18" s="9">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="BW18" s="9">
+        <v>2.75E-2</v>
+      </c>
+      <c r="BX18" s="9">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="BY18" s="9">
+        <v>4.58E-2</v>
+      </c>
+      <c r="BZ18" s="9">
+        <v>4.19E-2</v>
+      </c>
+      <c r="CA18" s="9">
+        <v>3.3399999999999999E-2</v>
+      </c>
+      <c r="CB18" s="9">
+        <v>6.2100000000000002E-2</v>
+      </c>
+      <c r="CC18" s="9">
+        <v>4.6699999999999998E-2</v>
+      </c>
+      <c r="CD18" s="9">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="CE18" s="9">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="CF18" s="9">
+        <v>8.1199999999999994E-2</v>
+      </c>
+      <c r="CG18" s="9">
+        <v>6.9900000000000004E-2</v>
+      </c>
+      <c r="CH18" s="9">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="CI18" s="9">
+        <v>1.47E-2</v>
+      </c>
+      <c r="CJ18" s="9">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="CK18" s="9">
+        <v>1.8100000000000002E-2</v>
+      </c>
+      <c r="CL18" s="9">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="CM18" s="9">
+        <v>1.6899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:91" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -4323,7 +5620,7 @@
       <c r="L19" s="3">
         <v>175</v>
       </c>
-      <c r="M19" s="25">
+      <c r="M19" s="24">
         <v>62</v>
       </c>
       <c r="N19" s="1">
@@ -4338,21 +5635,21 @@
       <c r="Q19" s="1">
         <v>24</v>
       </c>
-      <c r="R19" s="30"/>
+      <c r="R19" s="33"/>
       <c r="S19" s="3">
         <v>0</v>
       </c>
-      <c r="T19" s="30"/>
-      <c r="U19" s="15">
+      <c r="T19" s="33"/>
+      <c r="U19" s="14">
         <v>3.7133333333333331E-2</v>
       </c>
-      <c r="V19" s="15">
+      <c r="V19" s="14">
         <v>8.5466666666666677E-2</v>
       </c>
-      <c r="W19" s="15">
+      <c r="W19" s="14">
         <v>0.12956666666666669</v>
       </c>
-      <c r="X19" s="33"/>
+      <c r="X19" s="36"/>
       <c r="Y19" s="1">
         <v>5.142E-2</v>
       </c>
@@ -4368,7 +5665,7 @@
       <c r="AC19" s="1">
         <v>4.1359999999999994E-2</v>
       </c>
-      <c r="AD19" s="33"/>
+      <c r="AD19" s="36"/>
       <c r="AE19" s="1">
         <v>8.0519999999999994E-2</v>
       </c>
@@ -4384,7 +5681,7 @@
       <c r="AI19" s="1">
         <v>6.4680000000000001E-2</v>
       </c>
-      <c r="AJ19" s="33"/>
+      <c r="AJ19" s="36"/>
       <c r="AK19" s="1">
         <v>0.12355999999999998</v>
       </c>
@@ -4400,21 +5697,21 @@
       <c r="AO19" s="1">
         <v>4.632E-2</v>
       </c>
-      <c r="AP19" s="30"/>
+      <c r="AP19" s="33"/>
       <c r="AQ19" s="3">
         <v>5</v>
       </c>
-      <c r="AR19" s="36"/>
-      <c r="AS19" s="15">
+      <c r="AR19" s="39"/>
+      <c r="AS19" s="14">
         <v>3.5466666666666667E-2</v>
       </c>
-      <c r="AT19" s="15">
+      <c r="AT19" s="14">
         <v>8.0966666666666673E-2</v>
       </c>
-      <c r="AU19" s="15">
+      <c r="AU19" s="14">
         <v>0.13523333333333334</v>
       </c>
-      <c r="AV19" s="33"/>
+      <c r="AV19" s="36"/>
       <c r="AW19" s="1">
         <v>2.7739999999999997E-2</v>
       </c>
@@ -4430,7 +5727,7 @@
       <c r="BA19" s="1">
         <v>8.4440000000000001E-2</v>
       </c>
-      <c r="BB19" s="33"/>
+      <c r="BB19" s="36"/>
       <c r="BC19" s="1">
         <v>6.992000000000001E-2</v>
       </c>
@@ -4446,7 +5743,7 @@
       <c r="BG19" s="1">
         <v>6.5040000000000001E-2</v>
       </c>
-      <c r="BH19" s="33"/>
+      <c r="BH19" s="36"/>
       <c r="BI19" s="1">
         <v>0.11482000000000001</v>
       </c>
@@ -4463,15 +5760,81 @@
         <v>8.8479999999999989E-2</v>
       </c>
       <c r="BN19" s="27"/>
-      <c r="BO19" s="10">
+      <c r="BO19" s="1">
+        <v>0.12355999999999998</v>
+      </c>
+      <c r="BP19" s="1">
+        <v>8.0519999999999994E-2</v>
+      </c>
+      <c r="BQ19" s="1">
+        <v>0.11482000000000001</v>
+      </c>
+      <c r="BR19" s="1">
+        <v>6.992000000000001E-2</v>
+      </c>
+      <c r="BS19" s="30"/>
+      <c r="BT19" s="9">
         <v>3.2408000000000006E-2</v>
       </c>
-      <c r="BP19" s="10">
+      <c r="BU19" s="9">
         <v>3.2143999999999999E-2</v>
       </c>
-      <c r="BQ19" s="9"/>
-    </row>
-    <row r="20" spans="1:69" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="BV19" s="9">
+        <v>0.10979999999999999</v>
+      </c>
+      <c r="BW19" s="9">
+        <v>0.1411</v>
+      </c>
+      <c r="BX19" s="9">
+        <v>0.13780000000000001</v>
+      </c>
+      <c r="BY19" s="9">
+        <v>0.14030000000000001</v>
+      </c>
+      <c r="BZ19" s="9">
+        <v>0.13439999999999999</v>
+      </c>
+      <c r="CA19" s="9">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="CB19" s="9">
+        <v>0.1021</v>
+      </c>
+      <c r="CC19" s="9">
+        <v>7.1199999999999999E-2</v>
+      </c>
+      <c r="CD19" s="9">
+        <v>8.3099999999999993E-2</v>
+      </c>
+      <c r="CE19" s="9">
+        <v>7.9100000000000004E-2</v>
+      </c>
+      <c r="CF19" s="9">
+        <v>7.6600000000000001E-2</v>
+      </c>
+      <c r="CG19" s="9">
+        <v>8.72E-2</v>
+      </c>
+      <c r="CH19" s="9">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="CI19" s="9">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="CJ19" s="9">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="CK19" s="9">
+        <v>3.8100000000000002E-2</v>
+      </c>
+      <c r="CL19" s="9">
+        <v>3.8300000000000001E-2</v>
+      </c>
+      <c r="CM19" s="9">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="20" spans="1:91" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -4506,7 +5869,7 @@
       <c r="L20" s="3">
         <v>165</v>
       </c>
-      <c r="M20" s="25">
+      <c r="M20" s="24">
         <v>70</v>
       </c>
       <c r="N20" s="1">
@@ -4521,21 +5884,21 @@
       <c r="Q20" s="1">
         <v>7</v>
       </c>
-      <c r="R20" s="30"/>
+      <c r="R20" s="33"/>
       <c r="S20" s="3">
         <v>8</v>
       </c>
-      <c r="T20" s="30"/>
-      <c r="U20" s="15">
+      <c r="T20" s="33"/>
+      <c r="U20" s="14">
         <v>1.0533333333333334E-2</v>
       </c>
-      <c r="V20" s="15">
+      <c r="V20" s="14">
         <v>3.666666666666666E-2</v>
       </c>
-      <c r="W20" s="15">
+      <c r="W20" s="14">
         <v>1.3433333333333334E-2</v>
       </c>
-      <c r="X20" s="33"/>
+      <c r="X20" s="36"/>
       <c r="Y20" s="1">
         <v>1.192E-2</v>
       </c>
@@ -4551,7 +5914,7 @@
       <c r="AC20" s="1">
         <v>1.056E-2</v>
       </c>
-      <c r="AD20" s="33"/>
+      <c r="AD20" s="36"/>
       <c r="AE20" s="1">
         <v>2.4020000000000003E-2</v>
       </c>
@@ -4567,7 +5930,7 @@
       <c r="AI20" s="1">
         <v>1.592E-2</v>
       </c>
-      <c r="AJ20" s="33"/>
+      <c r="AJ20" s="36"/>
       <c r="AK20" s="1">
         <v>1.082E-2</v>
       </c>
@@ -4583,21 +5946,21 @@
       <c r="AO20" s="1">
         <v>8.5600000000000016E-3</v>
       </c>
-      <c r="AP20" s="30"/>
+      <c r="AP20" s="33"/>
       <c r="AQ20" s="3">
         <v>4</v>
       </c>
-      <c r="AR20" s="36"/>
-      <c r="AS20" s="15">
+      <c r="AR20" s="39"/>
+      <c r="AS20" s="14">
         <v>6.4333333333333326E-3</v>
       </c>
-      <c r="AT20" s="15">
+      <c r="AT20" s="14">
         <v>1.6766666666666666E-2</v>
       </c>
-      <c r="AU20" s="15">
+      <c r="AU20" s="14">
         <v>1.7066666666666667E-2</v>
       </c>
-      <c r="AV20" s="33"/>
+      <c r="AV20" s="36"/>
       <c r="AW20" s="1">
         <v>6.2800000000000009E-3</v>
       </c>
@@ -4613,7 +5976,7 @@
       <c r="BA20" s="1">
         <v>7.0400000000000003E-3</v>
       </c>
-      <c r="BB20" s="33"/>
+      <c r="BB20" s="36"/>
       <c r="BC20" s="1">
         <v>1.8319999999999999E-2</v>
       </c>
@@ -4629,7 +5992,7 @@
       <c r="BG20" s="1">
         <v>1.848E-2</v>
       </c>
-      <c r="BH20" s="33"/>
+      <c r="BH20" s="36"/>
       <c r="BI20" s="1">
         <v>1.4160000000000001E-2</v>
       </c>
@@ -4646,15 +6009,81 @@
         <v>2.452E-2</v>
       </c>
       <c r="BN20" s="27"/>
-      <c r="BO20" s="10">
+      <c r="BO20" s="1">
+        <v>1.082E-2</v>
+      </c>
+      <c r="BP20" s="1">
+        <v>2.4020000000000003E-2</v>
+      </c>
+      <c r="BQ20" s="1">
+        <v>1.4160000000000001E-2</v>
+      </c>
+      <c r="BR20" s="1">
+        <v>1.8319999999999999E-2</v>
+      </c>
+      <c r="BS20" s="30"/>
+      <c r="BT20" s="9">
         <v>3.0836000000000002E-2</v>
       </c>
-      <c r="BP20" s="10">
+      <c r="BU20" s="9">
         <v>3.0836000000000002E-2</v>
       </c>
-      <c r="BQ20" s="9"/>
-    </row>
-    <row r="21" spans="1:69" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="BV20" s="9">
+        <v>1.18E-2</v>
+      </c>
+      <c r="BW20" s="9">
+        <v>9.7000000000000003E-3</v>
+      </c>
+      <c r="BX20" s="9">
+        <v>1.8800000000000001E-2</v>
+      </c>
+      <c r="BY20" s="9">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="BZ20" s="9">
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="CA20" s="9">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="CB20" s="9">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="CC20" s="9">
+        <v>4.8399999999999999E-2</v>
+      </c>
+      <c r="CD20" s="9">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="CE20" s="9">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="CF20" s="9">
+        <v>1.43E-2</v>
+      </c>
+      <c r="CG20" s="9">
+        <v>1.32E-2</v>
+      </c>
+      <c r="CH20" s="9">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="CI20" s="9">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="CJ20" s="9">
+        <v>1.15E-2</v>
+      </c>
+      <c r="CK20" s="9">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="CL20" s="9">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="CM20" s="9">
+        <v>7.6E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:91" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -4689,7 +6118,7 @@
       <c r="L21" s="3">
         <v>177</v>
       </c>
-      <c r="M21" s="25">
+      <c r="M21" s="24">
         <v>79</v>
       </c>
       <c r="N21" s="1">
@@ -4704,28 +6133,46 @@
       <c r="Q21" s="1">
         <v>1</v>
       </c>
-      <c r="R21" s="31"/>
+      <c r="R21" s="34"/>
       <c r="S21" s="3"/>
-      <c r="T21" s="31"/>
-      <c r="X21" s="34"/>
-      <c r="AD21" s="34"/>
-      <c r="AJ21" s="34"/>
-      <c r="AP21" s="31"/>
+      <c r="T21" s="34"/>
+      <c r="X21" s="37"/>
+      <c r="AD21" s="37"/>
+      <c r="AJ21" s="37"/>
+      <c r="AP21" s="34"/>
       <c r="AQ21" s="3"/>
-      <c r="AR21" s="37"/>
-      <c r="AV21" s="34"/>
-      <c r="BB21" s="34"/>
-      <c r="BH21" s="34"/>
+      <c r="AR21" s="40"/>
+      <c r="AV21" s="37"/>
+      <c r="BB21" s="37"/>
+      <c r="BH21" s="37"/>
       <c r="BN21" s="28"/>
-      <c r="BO21" s="10">
+      <c r="BO21" s="9">
+        <v>6.9199999999999998E-2</v>
+      </c>
+      <c r="BP21" s="9">
+        <v>6.6040000000000001E-2</v>
+      </c>
+      <c r="BQ21" s="1">
+        <v>7.1859999999999993E-2</v>
+      </c>
+      <c r="BR21" s="9">
+        <v>0.10958</v>
+      </c>
+      <c r="BS21" s="31"/>
+      <c r="BT21" s="9">
         <v>9.7280000000000005E-3</v>
       </c>
-      <c r="BP21" s="10">
+      <c r="BU21" s="9">
         <v>8.7400000000000012E-3</v>
       </c>
-      <c r="BQ21" s="9"/>
-    </row>
-    <row r="22" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BV21" s="9"/>
+      <c r="BW21" s="9"/>
+      <c r="BX21" s="9"/>
+      <c r="BY21" s="9"/>
+      <c r="BZ21" s="9"/>
+      <c r="CA21" s="9"/>
+    </row>
+    <row r="22" spans="1:91" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>80</v>
       </c>
@@ -4737,33 +6184,69 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="5"/>
-      <c r="BO22" s="11">
+      <c r="BO22" s="1">
+        <v>4.614E-2</v>
+      </c>
+      <c r="BP22" s="9">
+        <v>3.918E-2</v>
+      </c>
+      <c r="BQ22" s="1">
+        <v>9.5100000000000004E-2</v>
+      </c>
+      <c r="BR22" s="9">
+        <v>4.99E-2</v>
+      </c>
+      <c r="BT22" s="10">
         <v>6.8392000000000008E-2</v>
       </c>
-      <c r="BP22" s="11">
+      <c r="BU22" s="10">
         <v>6.8392000000000008E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:91" x14ac:dyDescent="0.25">
       <c r="C23" s="3"/>
       <c r="M23" s="5"/>
-      <c r="BO23" s="10">
+      <c r="BO23" s="1">
+        <v>1.6879999999999999E-2</v>
+      </c>
+      <c r="BP23" s="9">
+        <v>6.6180000000000003E-2</v>
+      </c>
+      <c r="BQ23" s="1">
+        <v>4.9140000000000003E-2</v>
+      </c>
+      <c r="BR23" s="9">
+        <v>0.11348</v>
+      </c>
+      <c r="BT23" s="9">
         <v>3.9635999999999998E-2</v>
       </c>
-      <c r="BP23" s="10">
+      <c r="BU23" s="9">
         <v>3.9635999999999998E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:91" x14ac:dyDescent="0.25">
       <c r="M24" s="5"/>
-      <c r="BO24" s="10">
+      <c r="BO24" s="9">
+        <v>1.532E-2</v>
+      </c>
+      <c r="BP24" s="9">
+        <v>1.788E-2</v>
+      </c>
+      <c r="BQ24" s="1">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="BR24" s="9">
+        <v>2.605E-2</v>
+      </c>
+      <c r="BT24" s="9">
         <v>6.7591999999999999E-2</v>
       </c>
-      <c r="BP24" s="10">
+      <c r="BU24" s="9">
         <v>6.7591999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:91" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>63</v>
       </c>
@@ -4776,14 +6259,26 @@
       <c r="L25" s="4"/>
       <c r="M25" s="5"/>
       <c r="N25" s="4"/>
-      <c r="BO25" s="10">
+      <c r="BO25" s="9">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="BP25" s="9">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="BQ25" s="1">
+        <v>4.5319999999999999E-2</v>
+      </c>
+      <c r="BR25" s="9">
+        <v>5.4820000000000001E-2</v>
+      </c>
+      <c r="BT25" s="9">
         <v>1.9464000000000002E-2</v>
       </c>
-      <c r="BP25" s="10">
+      <c r="BU25" s="9">
         <v>1.9464000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:91" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>64</v>
       </c>
@@ -4796,14 +6291,26 @@
       <c r="L26" s="4"/>
       <c r="M26" s="5"/>
       <c r="N26" s="4"/>
-      <c r="BO26" s="10">
+      <c r="BO26" s="9">
+        <v>8.6240000000000011E-2</v>
+      </c>
+      <c r="BP26" s="1">
+        <v>8.3680000000000004E-2</v>
+      </c>
+      <c r="BQ26" s="1">
+        <v>0.12825999999999999</v>
+      </c>
+      <c r="BR26" s="1">
+        <v>5.1720000000000002E-2</v>
+      </c>
+      <c r="BT26" s="9">
         <v>3.4611999999999997E-2</v>
       </c>
-      <c r="BP26" s="10">
+      <c r="BU26" s="9">
         <v>3.4611999999999997E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:91" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>65</v>
       </c>
@@ -4816,38 +6323,74 @@
       <c r="L27" s="4"/>
       <c r="M27" s="5"/>
       <c r="N27" s="4"/>
-      <c r="BO27" s="10">
+      <c r="BO27" s="1">
+        <v>0.11778</v>
+      </c>
+      <c r="BP27" s="1">
+        <v>5.9380000000000009E-2</v>
+      </c>
+      <c r="BQ27" s="1">
+        <v>0.10935999999999998</v>
+      </c>
+      <c r="BR27" s="1">
+        <v>0.18284</v>
+      </c>
+      <c r="BT27" s="9">
         <v>0.107124</v>
       </c>
-      <c r="BP27" s="10">
+      <c r="BU27" s="9">
         <v>0.107124</v>
       </c>
     </row>
-    <row r="28" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:91" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>66</v>
       </c>
       <c r="M28" s="5"/>
-      <c r="BO28" s="10">
+      <c r="BO28" s="9">
+        <v>3.1E-2</v>
+      </c>
+      <c r="BP28" s="1">
+        <v>2.0900000000000002E-2</v>
+      </c>
+      <c r="BQ28" s="1">
+        <v>5.7900000000000007E-2</v>
+      </c>
+      <c r="BR28" s="1">
+        <v>2.5840000000000002E-2</v>
+      </c>
+      <c r="BT28" s="9">
         <v>4.9144E-2</v>
       </c>
-      <c r="BP28" s="10">
+      <c r="BU28" s="9">
         <v>4.9144E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:91" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>67</v>
       </c>
       <c r="M29" s="5"/>
-      <c r="BO29" s="10">
+      <c r="BO29" s="9">
+        <v>3.2439999999999997E-2</v>
+      </c>
+      <c r="BP29" s="1">
+        <v>0.11464000000000001</v>
+      </c>
+      <c r="BQ29" s="1">
+        <v>6.2859999999999999E-2</v>
+      </c>
+      <c r="BR29" s="1">
+        <v>0.18820000000000001</v>
+      </c>
+      <c r="BT29" s="9">
         <v>0.11118000000000001</v>
       </c>
-      <c r="BP29" s="10">
+      <c r="BU29" s="9">
         <v>0.11118000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:91" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>68</v>
       </c>
@@ -4859,38 +6402,74 @@
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="5"/>
-      <c r="BO30" s="10">
+      <c r="BO30" s="9">
+        <v>3.6159999999999998E-2</v>
+      </c>
+      <c r="BP30" s="1">
+        <v>5.3479999999999993E-2</v>
+      </c>
+      <c r="BQ30" s="1">
+        <v>2.9320000000000002E-2</v>
+      </c>
+      <c r="BR30" s="1">
+        <v>6.4640000000000003E-2</v>
+      </c>
+      <c r="BT30" s="9">
         <v>2.6579999999999999E-2</v>
       </c>
-      <c r="BP30" s="10">
+      <c r="BU30" s="9">
         <v>2.6579999999999999E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:91" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>69</v>
       </c>
       <c r="M31" s="5"/>
-      <c r="BO31" s="10">
+      <c r="BO31" s="1">
+        <v>8.482000000000002E-2</v>
+      </c>
+      <c r="BP31" s="1">
+        <v>6.7600000000000007E-2</v>
+      </c>
+      <c r="BQ31" s="1">
+        <v>0.10438</v>
+      </c>
+      <c r="BR31" s="1">
+        <v>0.10879999999999998</v>
+      </c>
+      <c r="BT31" s="9">
         <v>4.8996000000000005E-2</v>
       </c>
-      <c r="BP31" s="10">
+      <c r="BU31" s="9">
         <v>4.8996000000000005E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:91" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>70</v>
       </c>
       <c r="M32" s="5"/>
-      <c r="BO32" s="11">
+      <c r="BO32" s="1">
+        <v>1.4620000000000003E-2</v>
+      </c>
+      <c r="BP32" s="1">
+        <v>3.576E-2</v>
+      </c>
+      <c r="BQ32" s="1">
+        <v>3.1359999999999999E-2</v>
+      </c>
+      <c r="BR32" s="1">
+        <v>4.5620000000000001E-2</v>
+      </c>
+      <c r="BT32" s="10">
         <v>6.3263999999999987E-2</v>
       </c>
-      <c r="BP32" s="11">
+      <c r="BU32" s="10">
         <v>6.3263999999999987E-2</v>
       </c>
     </row>
-    <row r="33" spans="3:68" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:73" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>71</v>
       </c>
@@ -4902,38 +6481,74 @@
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="5"/>
-      <c r="BO33" s="10">
+      <c r="BO33" s="17">
+        <v>0.13950000000000001</v>
+      </c>
+      <c r="BP33" s="17">
+        <v>7.0180000000000006E-2</v>
+      </c>
+      <c r="BQ33" s="17">
+        <v>0.15690000000000001</v>
+      </c>
+      <c r="BR33" s="17">
+        <v>7.9740000000000005E-2</v>
+      </c>
+      <c r="BT33" s="9">
         <v>4.5428000000000003E-2</v>
       </c>
-      <c r="BP33" s="10">
+      <c r="BU33" s="9">
         <v>4.5428000000000003E-2</v>
       </c>
     </row>
-    <row r="34" spans="3:68" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:73" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>72</v>
       </c>
       <c r="M34" s="5"/>
-      <c r="BO34" s="10">
+      <c r="BO34" s="1">
+        <v>0.10356600000000001</v>
+      </c>
+      <c r="BP34" s="1">
+        <v>9.2159999999999992E-2</v>
+      </c>
+      <c r="BQ34" s="1">
+        <v>0.13372000000000001</v>
+      </c>
+      <c r="BR34" s="1">
+        <v>6.7799999999999999E-2</v>
+      </c>
+      <c r="BT34" s="9">
         <v>1.942E-2</v>
       </c>
-      <c r="BP34" s="10">
+      <c r="BU34" s="9">
         <v>1.942E-2</v>
       </c>
     </row>
-    <row r="35" spans="3:68" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:73" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>73</v>
       </c>
       <c r="M35" s="5"/>
-      <c r="BO35" s="10">
+      <c r="BO35" s="1">
+        <v>1.34E-2</v>
+      </c>
+      <c r="BP35" s="1">
+        <v>3.4040000000000001E-2</v>
+      </c>
+      <c r="BQ35" s="1">
+        <v>2.8339999999999997E-2</v>
+      </c>
+      <c r="BR35" s="1">
+        <v>4.0759999999999998E-2</v>
+      </c>
+      <c r="BT35" s="9">
         <v>1.4044000000000001E-2</v>
       </c>
-      <c r="BP35" s="10">
+      <c r="BU35" s="9">
         <v>1.4044000000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="3:68" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:73" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>74</v>
       </c>
@@ -4945,38 +6560,74 @@
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="5"/>
-      <c r="BO36" s="10">
+      <c r="BO36" s="1">
+        <v>0.10556</v>
+      </c>
+      <c r="BP36" s="1">
+        <v>0.14835999999999999</v>
+      </c>
+      <c r="BQ36" s="1">
+        <v>0.32857999999999998</v>
+      </c>
+      <c r="BR36" s="1">
+        <v>0.12356</v>
+      </c>
+      <c r="BT36" s="9">
         <v>3.0168E-2</v>
       </c>
-      <c r="BP36" s="10">
+      <c r="BU36" s="9">
         <v>3.0168E-2</v>
       </c>
     </row>
-    <row r="37" spans="3:68" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:73" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
         <v>75</v>
       </c>
       <c r="M37" s="5"/>
-      <c r="BO37" s="10">
+      <c r="BO37" s="1">
+        <v>3.6720000000000003E-2</v>
+      </c>
+      <c r="BP37" s="1">
+        <v>4.9579999999999999E-2</v>
+      </c>
+      <c r="BQ37" s="1">
+        <v>4.5680000000000005E-2</v>
+      </c>
+      <c r="BR37" s="1">
+        <v>7.4779999999999999E-2</v>
+      </c>
+      <c r="BT37" s="9">
         <v>6.5979999999999997E-2</v>
       </c>
-      <c r="BP37" s="10">
+      <c r="BU37" s="9">
         <v>6.5979999999999997E-2</v>
       </c>
     </row>
-    <row r="38" spans="3:68" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:73" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
         <v>76</v>
       </c>
       <c r="M38" s="5"/>
-      <c r="BO38" s="10">
+      <c r="BO38" s="1">
+        <v>8.702E-2</v>
+      </c>
+      <c r="BP38" s="1">
+        <v>7.3080000000000006E-2</v>
+      </c>
+      <c r="BQ38" s="1">
+        <v>0.11918000000000002</v>
+      </c>
+      <c r="BR38" s="1">
+        <v>8.4059999999999996E-2</v>
+      </c>
+      <c r="BT38" s="9">
         <v>9.4700000000000006E-2</v>
       </c>
-      <c r="BP38" s="10">
+      <c r="BU38" s="9">
         <v>9.4700000000000006E-2</v>
       </c>
     </row>
-    <row r="39" spans="3:68" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:73" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>77</v>
       </c>
@@ -4987,36 +6638,72 @@
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
-      <c r="BO39" s="10">
+      <c r="BO39" s="1">
+        <v>9.0799999999999995E-3</v>
+      </c>
+      <c r="BP39" s="1">
+        <v>1.898E-2</v>
+      </c>
+      <c r="BQ39" s="1">
+        <v>1.464E-2</v>
+      </c>
+      <c r="BR39" s="1">
+        <v>1.9479999999999997E-2</v>
+      </c>
+      <c r="BT39" s="9">
         <v>4.7204000000000003E-2</v>
       </c>
-      <c r="BP39" s="10">
+      <c r="BU39" s="9">
         <v>4.7204000000000003E-2</v>
       </c>
     </row>
-    <row r="40" spans="3:68" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:73" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>78</v>
       </c>
-      <c r="BO40" s="10">
+      <c r="BO40" s="9">
+        <v>5.6779999999999997E-2</v>
+      </c>
+      <c r="BP40" s="9">
+        <v>7.4380000000000002E-2</v>
+      </c>
+      <c r="BQ40" s="1">
+        <v>5.5480000000000002E-2</v>
+      </c>
+      <c r="BR40" s="9">
+        <v>0.10285999999999999</v>
+      </c>
+      <c r="BT40" s="9">
         <v>2.0868000000000005E-2</v>
       </c>
-      <c r="BP40" s="10">
+      <c r="BU40" s="9">
         <v>2.0868000000000005E-2</v>
       </c>
     </row>
-    <row r="41" spans="3:68" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:73" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>79</v>
       </c>
-      <c r="BO41" s="10">
+      <c r="BO41" s="1">
+        <v>4.428E-2</v>
+      </c>
+      <c r="BP41" s="9">
+        <v>4.0379999999999999E-2</v>
+      </c>
+      <c r="BQ41" s="1">
+        <v>9.5280000000000004E-2</v>
+      </c>
+      <c r="BR41" s="9">
+        <v>5.842E-2</v>
+      </c>
+      <c r="BT41" s="9">
         <v>4.1180000000000001E-2</v>
       </c>
-      <c r="BP41" s="10">
+      <c r="BU41" s="9">
         <v>4.1180000000000001E-2</v>
       </c>
     </row>
-    <row r="42" spans="3:68" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:73" x14ac:dyDescent="0.25">
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -5024,10 +6711,778 @@
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
+      <c r="BO42" s="1">
+        <v>1.9779999999999999E-2</v>
+      </c>
+      <c r="BP42" s="9">
+        <v>7.0940000000000003E-2</v>
+      </c>
+      <c r="BQ42" s="1">
+        <v>4.7460000000000002E-2</v>
+      </c>
+      <c r="BR42" s="9">
+        <v>0.11126</v>
+      </c>
+    </row>
+    <row r="43" spans="3:73" x14ac:dyDescent="0.25">
+      <c r="BO43" s="9">
+        <v>1.218E-2</v>
+      </c>
+      <c r="BP43" s="9">
+        <v>1.634E-2</v>
+      </c>
+      <c r="BQ43" s="1">
+        <v>1.898E-2</v>
+      </c>
+      <c r="BR43" s="9">
+        <v>2.5100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="3:73" x14ac:dyDescent="0.25">
+      <c r="BO44" s="9">
+        <v>2.896E-2</v>
+      </c>
+      <c r="BP44" s="9">
+        <v>3.39E-2</v>
+      </c>
+      <c r="BQ44" s="1">
+        <v>4.0160000000000001E-2</v>
+      </c>
+      <c r="BR44" s="9">
+        <v>4.6240000000000003E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="3:73" x14ac:dyDescent="0.25">
+      <c r="BO45" s="9">
+        <v>7.2639999999999996E-2</v>
+      </c>
+      <c r="BP45" s="1">
+        <v>7.9699999999999993E-2</v>
+      </c>
+      <c r="BQ45" s="1">
+        <v>0.13381999999999999</v>
+      </c>
+      <c r="BR45" s="1">
+        <v>5.3079999999999995E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="3:73" x14ac:dyDescent="0.25">
+      <c r="BO46" s="1">
+        <v>0.100782</v>
+      </c>
+      <c r="BP46" s="1">
+        <v>5.0160000000000003E-2</v>
+      </c>
+      <c r="BQ46" s="1">
+        <v>0.11878</v>
+      </c>
+      <c r="BR46" s="1">
+        <v>0.10174000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="3:73" x14ac:dyDescent="0.25">
+      <c r="BO47" s="9">
+        <v>2.7979999999999998E-2</v>
+      </c>
+      <c r="BP47" s="1">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="BQ47" s="1">
+        <v>5.0039999999999994E-2</v>
+      </c>
+      <c r="BR47" s="1">
+        <v>2.716E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="3:73" x14ac:dyDescent="0.25">
+      <c r="BO48" s="9">
+        <v>3.2619999999999996E-2</v>
+      </c>
+      <c r="BP48" s="1">
+        <v>0.10303999999999999</v>
+      </c>
+      <c r="BQ48" s="1">
+        <v>6.3959999999999989E-2</v>
+      </c>
+      <c r="BR48" s="1">
+        <v>0.16431999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO49" s="9">
+        <v>3.6240000000000001E-2</v>
+      </c>
+      <c r="BP49" s="1">
+        <v>5.008E-2</v>
+      </c>
+      <c r="BQ49" s="1">
+        <v>3.2100000000000004E-2</v>
+      </c>
+      <c r="BR49" s="1">
+        <v>6.6320000000000004E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO50" s="1">
+        <v>8.8920000000000013E-2</v>
+      </c>
+      <c r="BP50" s="1">
+        <v>5.364E-2</v>
+      </c>
+      <c r="BQ50" s="1">
+        <v>9.9879999999999997E-2</v>
+      </c>
+      <c r="BR50" s="1">
+        <v>8.9499999999999996E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO51" s="1">
+        <v>1.7059999999999999E-2</v>
+      </c>
+      <c r="BP51" s="1">
+        <v>3.5279999999999992E-2</v>
+      </c>
+      <c r="BQ51" s="1">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="BR51" s="1">
+        <v>5.16E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO52" s="17">
+        <v>0.11346000000000001</v>
+      </c>
+      <c r="BP52" s="17">
+        <v>5.4100000000000002E-2</v>
+      </c>
+      <c r="BQ52" s="17">
+        <v>0.13533999999999999</v>
+      </c>
+      <c r="BR52" s="17">
+        <v>7.6780000000000001E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO53" s="1">
+        <v>0.11039000000000002</v>
+      </c>
+      <c r="BP53" s="1">
+        <v>8.6919999999999997E-2</v>
+      </c>
+      <c r="BQ53" s="1">
+        <v>0.14974000000000001</v>
+      </c>
+      <c r="BR53" s="1">
+        <v>7.986E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO54" s="1">
+        <v>1.1820000000000001E-2</v>
+      </c>
+      <c r="BP54" s="1">
+        <v>2.7559999999999994E-2</v>
+      </c>
+      <c r="BQ54" s="1">
+        <v>2.554E-2</v>
+      </c>
+      <c r="BR54" s="1">
+        <v>4.1939999999999998E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO55" s="1">
+        <v>0.12012</v>
+      </c>
+      <c r="BP55" s="1">
+        <v>0.16980000000000001</v>
+      </c>
+      <c r="BQ55" s="1">
+        <v>0.22123999999999999</v>
+      </c>
+      <c r="BR55" s="1">
+        <v>0.10186000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO56" s="1">
+        <v>3.4020000000000009E-2</v>
+      </c>
+      <c r="BP56" s="1">
+        <v>4.9060000000000006E-2</v>
+      </c>
+      <c r="BQ56" s="1">
+        <v>4.4159999999999998E-2</v>
+      </c>
+      <c r="BR56" s="1">
+        <v>6.9399999999999989E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO57" s="1">
+        <v>8.6559999999999998E-2</v>
+      </c>
+      <c r="BP57" s="1">
+        <v>5.9760000000000001E-2</v>
+      </c>
+      <c r="BQ57" s="1">
+        <v>0.10602</v>
+      </c>
+      <c r="BR57" s="1">
+        <v>6.6700000000000009E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO58" s="1">
+        <v>1.0960000000000001E-2</v>
+      </c>
+      <c r="BP58" s="1">
+        <v>2.1659999999999999E-2</v>
+      </c>
+      <c r="BQ58" s="1">
+        <v>1.366E-2</v>
+      </c>
+      <c r="BR58" s="1">
+        <v>2.0180000000000003E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO59" s="9">
+        <v>6.4860000000000001E-2</v>
+      </c>
+      <c r="BP59" s="9">
+        <v>6.336E-2</v>
+      </c>
+      <c r="BQ59" s="1">
+        <v>7.6240000000000002E-2</v>
+      </c>
+      <c r="BR59" s="9">
+        <v>0.13222</v>
+      </c>
+    </row>
+    <row r="60" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO60" s="1">
+        <v>4.138E-2</v>
+      </c>
+      <c r="BP60" s="9">
+        <v>3.4139999999999997E-2</v>
+      </c>
+      <c r="BQ60" s="1">
+        <v>9.7420000000000007E-2</v>
+      </c>
+      <c r="BR60" s="9">
+        <v>4.6820000000000001E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO61" s="1">
+        <v>1.7139999999999999E-2</v>
+      </c>
+      <c r="BP61" s="9">
+        <v>6.0319999999999999E-2</v>
+      </c>
+      <c r="BQ61" s="1">
+        <v>4.4519999999999997E-2</v>
+      </c>
+      <c r="BR61" s="9">
+        <v>0.10316</v>
+      </c>
+    </row>
+    <row r="62" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO62" s="9">
+        <v>1.204E-2</v>
+      </c>
+      <c r="BP62" s="9">
+        <v>1.506E-2</v>
+      </c>
+      <c r="BQ62" s="1">
+        <v>1.9560000000000001E-2</v>
+      </c>
+      <c r="BR62" s="9">
+        <v>3.5520000000000003E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO63" s="9">
+        <v>2.7179999999999999E-2</v>
+      </c>
+      <c r="BP63" s="9">
+        <v>3.3279999999999997E-2</v>
+      </c>
+      <c r="BQ63" s="1">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="BR63" s="9">
+        <v>5.2519999999999997E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO64" s="9">
+        <v>7.2959999999999997E-2</v>
+      </c>
+      <c r="BP64" s="1">
+        <v>8.2140000000000005E-2</v>
+      </c>
+      <c r="BQ64" s="1">
+        <v>0.12245999999999999</v>
+      </c>
+      <c r="BR64" s="1">
+        <v>5.5359999999999999E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO65" s="1">
+        <v>0.10698000000000001</v>
+      </c>
+      <c r="BP65" s="1">
+        <v>5.2420000000000001E-2</v>
+      </c>
+      <c r="BQ65" s="1">
+        <v>0.10102</v>
+      </c>
+      <c r="BR65" s="1">
+        <v>7.1959999999999996E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO66" s="9">
+        <v>2.6040000000000001E-2</v>
+      </c>
+      <c r="BP66" s="1">
+        <v>1.83E-2</v>
+      </c>
+      <c r="BQ66" s="1">
+        <v>4.8900000000000006E-2</v>
+      </c>
+      <c r="BR66" s="1">
+        <v>2.2119999999999994E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO67" s="9">
+        <v>3.5240000000000007E-2</v>
+      </c>
+      <c r="BP67" s="1">
+        <v>0.12908</v>
+      </c>
+      <c r="BQ67" s="1">
+        <v>7.9420000000000004E-2</v>
+      </c>
+      <c r="BR67" s="1">
+        <v>0.20444000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO68" s="9">
+        <v>3.4820000000000004E-2</v>
+      </c>
+      <c r="BP68" s="1">
+        <v>5.0599999999999999E-2</v>
+      </c>
+      <c r="BQ68" s="1">
+        <v>3.1520000000000006E-2</v>
+      </c>
+      <c r="BR68" s="1">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO69" s="1">
+        <v>0.11268</v>
+      </c>
+      <c r="BP69" s="1">
+        <v>5.3380000000000004E-2</v>
+      </c>
+      <c r="BQ69" s="1">
+        <v>9.953999999999999E-2</v>
+      </c>
+      <c r="BR69" s="1">
+        <v>8.8739999999999999E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO70" s="1">
+        <v>1.6279999999999999E-2</v>
+      </c>
+      <c r="BP70" s="1">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="BQ70" s="1">
+        <v>3.8120000000000001E-2</v>
+      </c>
+      <c r="BR70" s="1">
+        <v>5.4859999999999999E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO71" s="17">
+        <v>0.11588</v>
+      </c>
+      <c r="BP71" s="17">
+        <v>7.0739999999999997E-2</v>
+      </c>
+      <c r="BQ71" s="17">
+        <v>0.14294000000000001</v>
+      </c>
+      <c r="BR71" s="17">
+        <v>8.3599999999999994E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO72" s="1">
+        <v>0.11466000000000001</v>
+      </c>
+      <c r="BP72" s="1">
+        <v>9.0340000000000004E-2</v>
+      </c>
+      <c r="BQ72" s="1">
+        <v>0.12278</v>
+      </c>
+      <c r="BR72" s="1">
+        <v>7.8039999999999998E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO73" s="1">
+        <v>1.3019999999999999E-2</v>
+      </c>
+      <c r="BP73" s="1">
+        <v>3.0479999999999997E-2</v>
+      </c>
+      <c r="BQ73" s="1">
+        <v>2.5340000000000001E-2</v>
+      </c>
+      <c r="BR73" s="1">
+        <v>3.4740000000000007E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO74" s="1">
+        <v>0.13311999999999999</v>
+      </c>
+      <c r="BP74" s="1">
+        <v>0.14912</v>
+      </c>
+      <c r="BQ74" s="1">
+        <v>0.27504000000000001</v>
+      </c>
+      <c r="BR74" s="1">
+        <v>0.10706</v>
+      </c>
+    </row>
+    <row r="75" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO75" s="1">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="BP75" s="1">
+        <v>4.598E-2</v>
+      </c>
+      <c r="BQ75" s="1">
+        <v>3.9400000000000004E-2</v>
+      </c>
+      <c r="BR75" s="1">
+        <v>6.6880000000000009E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO76" s="1">
+        <v>7.442E-2</v>
+      </c>
+      <c r="BP76" s="1">
+        <v>6.3039999999999999E-2</v>
+      </c>
+      <c r="BQ76" s="1">
+        <v>0.1052</v>
+      </c>
+      <c r="BR76" s="1">
+        <v>6.9779999999999995E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO77" s="1">
+        <v>8.8400000000000006E-3</v>
+      </c>
+      <c r="BP77" s="1">
+        <v>1.7800000000000003E-2</v>
+      </c>
+      <c r="BQ77" s="1">
+        <v>1.338E-2</v>
+      </c>
+      <c r="BR77" s="1">
+        <v>1.958E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO78" s="9">
+        <v>5.6599999999999998E-2</v>
+      </c>
+      <c r="BP78" s="9">
+        <v>6.5939999999999999E-2</v>
+      </c>
+      <c r="BQ78" s="1">
+        <v>7.1480000000000002E-2</v>
+      </c>
+      <c r="BR78" s="9">
+        <v>0.1113</v>
+      </c>
+    </row>
+    <row r="79" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO79" s="1">
+        <v>5.1239999999999994E-2</v>
+      </c>
+      <c r="BP79" s="9">
+        <v>4.2100000000000005E-2</v>
+      </c>
+      <c r="BQ79" s="1">
+        <v>9.8820000000000005E-2</v>
+      </c>
+      <c r="BR79" s="9">
+        <v>4.8760000000000005E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO80" s="1">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="BP80" s="9">
+        <v>6.6659999999999997E-2</v>
+      </c>
+      <c r="BQ80" s="1">
+        <v>4.8180000000000001E-2</v>
+      </c>
+      <c r="BR80" s="9">
+        <v>0.12090000000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO81" s="9">
+        <v>1.4100000000000001E-2</v>
+      </c>
+      <c r="BP81" s="9">
+        <v>3.0000000000000006E-2</v>
+      </c>
+      <c r="BQ81" s="1">
+        <v>2.104E-2</v>
+      </c>
+      <c r="BR81" s="9">
+        <v>2.2449999999999998E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO82" s="9">
+        <v>2.1539999999999997E-2</v>
+      </c>
+      <c r="BP82" s="9">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="BQ82" s="1">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="BR82" s="9">
+        <v>4.9080000000000006E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO83" s="9">
+        <v>5.4647999999999995E-2</v>
+      </c>
+      <c r="BP83" s="1">
+        <v>8.6399999999999991E-2</v>
+      </c>
+      <c r="BQ83" s="1">
+        <v>0.13346</v>
+      </c>
+      <c r="BR83" s="1">
+        <v>5.1519999999999996E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO84" s="1">
+        <v>0.11194</v>
+      </c>
+      <c r="BP84" s="1">
+        <v>5.9880000000000003E-2</v>
+      </c>
+      <c r="BQ84" s="1">
+        <v>0.12172000000000001</v>
+      </c>
+      <c r="BR84" s="1">
+        <v>0.22664000000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO85" s="9">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="BP85" s="1">
+        <v>2.0639999999999999E-2</v>
+      </c>
+      <c r="BQ85" s="1">
+        <v>4.7540000000000006E-2</v>
+      </c>
+      <c r="BR85" s="1">
+        <v>2.2700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO86" s="9">
+        <v>3.4419999999999999E-2</v>
+      </c>
+      <c r="BP86" s="1">
+        <v>0.12718000000000002</v>
+      </c>
+      <c r="BQ86" s="1">
+        <v>6.9040000000000004E-2</v>
+      </c>
+      <c r="BR86" s="1">
+        <v>0.19668000000000002</v>
+      </c>
+    </row>
+    <row r="87" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO87" s="9">
+        <v>3.6059999999999995E-2</v>
+      </c>
+      <c r="BP87" s="1">
+        <v>4.8420000000000005E-2</v>
+      </c>
+      <c r="BQ87" s="1">
+        <v>3.798E-2</v>
+      </c>
+      <c r="BR87" s="1">
+        <v>6.0000000000000012E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO88" s="1">
+        <v>0.10485999999999999</v>
+      </c>
+      <c r="BP88" s="1">
+        <v>6.3339999999999994E-2</v>
+      </c>
+      <c r="BQ88" s="1">
+        <v>0.10189999999999999</v>
+      </c>
+      <c r="BR88" s="1">
+        <v>8.6159999999999987E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO89" s="1">
+        <v>1.5559999999999999E-2</v>
+      </c>
+      <c r="BP89" s="1">
+        <v>4.0599999999999997E-2</v>
+      </c>
+      <c r="BQ89" s="1">
+        <v>3.9660000000000001E-2</v>
+      </c>
+      <c r="BR89" s="1">
+        <v>5.7179999999999995E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO90" s="17">
+        <v>0.10154000000000001</v>
+      </c>
+      <c r="BP90" s="17">
+        <v>5.528000000000001E-2</v>
+      </c>
+      <c r="BQ90" s="17">
+        <v>0.12074</v>
+      </c>
+      <c r="BR90" s="17">
+        <v>7.9820000000000002E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO91" s="1">
+        <v>0.12581999999999999</v>
+      </c>
+      <c r="BP91" s="1">
+        <v>8.0140000000000003E-2</v>
+      </c>
+      <c r="BQ91" s="1">
+        <v>0.13372000000000001</v>
+      </c>
+      <c r="BR91" s="1">
+        <v>8.5080000000000003E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO92" s="1">
+        <v>1.1600000000000003E-2</v>
+      </c>
+      <c r="BP92" s="1">
+        <v>2.9839999999999998E-2</v>
+      </c>
+      <c r="BQ92" s="1">
+        <v>2.0459999999999999E-2</v>
+      </c>
+      <c r="BR92" s="1">
+        <v>3.6339999999999997E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO93" s="1">
+        <v>0.11734</v>
+      </c>
+      <c r="BP93" s="1">
+        <v>0.12501999999999999</v>
+      </c>
+      <c r="BQ93" s="1">
+        <v>0.29236000000000006</v>
+      </c>
+      <c r="BR93" s="1">
+        <v>0.1192</v>
+      </c>
+    </row>
+    <row r="94" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO94" s="1">
+        <v>2.8339999999999997E-2</v>
+      </c>
+      <c r="BP94" s="1">
+        <v>4.7219999999999998E-2</v>
+      </c>
+      <c r="BQ94" s="1">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="BR94" s="1">
+        <v>7.282000000000001E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO95" s="1">
+        <v>4.632E-2</v>
+      </c>
+      <c r="BP95" s="1">
+        <v>6.4680000000000001E-2</v>
+      </c>
+      <c r="BQ95" s="1">
+        <v>8.8479999999999989E-2</v>
+      </c>
+      <c r="BR95" s="1">
+        <v>6.5040000000000001E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="67:70" x14ac:dyDescent="0.25">
+      <c r="BO96" s="1">
+        <v>8.5600000000000016E-3</v>
+      </c>
+      <c r="BP96" s="1">
+        <v>1.592E-2</v>
+      </c>
+      <c r="BQ96" s="1">
+        <v>2.452E-2</v>
+      </c>
+      <c r="BR96" s="1">
+        <v>1.848E-2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="BN1:BN21"/>
+    <mergeCell ref="BS1:BS21"/>
     <mergeCell ref="R2:R21"/>
     <mergeCell ref="T2:T21"/>
     <mergeCell ref="X1:X21"/>
